--- a/scripts/music.xlsx
+++ b/scripts/music.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13500"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$658</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$673</definedName>
   </definedNames>
   <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2235" uniqueCount="1085">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2301" uniqueCount="1112">
   <si>
     <t>歌名</t>
   </si>
@@ -3370,6 +3370,87 @@
   </si>
   <si>
     <t>卓文萱/曹格</t>
+  </si>
+  <si>
+    <t>白石溪</t>
+  </si>
+  <si>
+    <t>所念皆星河</t>
+  </si>
+  <si>
+    <t>巴啦啦小魔仙</t>
+  </si>
+  <si>
+    <t>A2A</t>
+  </si>
+  <si>
+    <t>生命所谓的意义</t>
+  </si>
+  <si>
+    <t>苏州河</t>
+  </si>
+  <si>
+    <t>薛凯琪</t>
+  </si>
+  <si>
+    <t>Little Wish</t>
+  </si>
+  <si>
+    <t>塞壬唱片-MSR/Sincere</t>
+  </si>
+  <si>
+    <t>彗星</t>
+  </si>
+  <si>
+    <t>白鲨JAWS</t>
+  </si>
+  <si>
+    <t>匿名的好友</t>
+  </si>
+  <si>
+    <t>我的我</t>
+  </si>
+  <si>
+    <t>袁一琦</t>
+  </si>
+  <si>
+    <t>新航路</t>
+  </si>
+  <si>
+    <t>大小孩</t>
+  </si>
+  <si>
+    <t>很需要</t>
+  </si>
+  <si>
+    <t>颜人中</t>
+  </si>
+  <si>
+    <t>Bye bad bye</t>
+  </si>
+  <si>
+    <t>愿与愁</t>
+  </si>
+  <si>
+    <t>星愿</t>
+  </si>
+  <si>
+    <t>骑士</t>
+  </si>
+  <si>
+    <t>after 17</t>
+  </si>
+  <si>
+    <t>女神之袂</t>
+  </si>
+  <si>
+    <t>你是我</t>
+  </si>
+  <si>
+    <t>干物女</t>
+  </si>
+  <si>
+    <t>月光</t>
   </si>
 </sst>
 </file>
@@ -4590,12 +4671,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F1082"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="61.6296296296296" customWidth="1"/>
+    <col min="1" max="1" width="61.6333333333333" customWidth="1"/>
     <col min="2" max="2" width="26.75" customWidth="1"/>
     <col min="4" max="4" width="7.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="20.8796296296296" customWidth="1"/>
+    <col min="5" max="5" width="20.8833333333333" customWidth="1"/>
     <col min="6" max="6" width="20" style="3" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4676,7 +4757,6 @@
       <c r="C6" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="2"/>
       <c r="E6" t="s">
         <v>15</v>
       </c>
@@ -4804,7 +4884,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" ht="15.6" spans="1:3">
+    <row r="18" ht="15" spans="1:3">
       <c r="A18" s="12" t="s">
         <v>28</v>
       </c>
@@ -4902,7 +4982,6 @@
       <c r="C26" t="s">
         <v>8</v>
       </c>
-      <c r="D26" s="2"/>
       <c r="E26" t="s">
         <v>39</v>
       </c>
@@ -4953,7 +5032,6 @@
       <c r="C30" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D30" s="2"/>
       <c r="E30" s="9"/>
     </row>
     <row r="31" spans="1:4">
@@ -5383,7 +5461,6 @@
       <c r="C64" t="s">
         <v>8</v>
       </c>
-      <c r="D64" s="2"/>
       <c r="E64" t="s">
         <v>114</v>
       </c>
@@ -5431,7 +5508,6 @@
       <c r="C68" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D68" s="2"/>
       <c r="E68" s="9"/>
     </row>
     <row r="69" spans="1:4">
@@ -5871,7 +5947,6 @@
       <c r="C98" t="s">
         <v>8</v>
       </c>
-      <c r="D98" s="2"/>
       <c r="E98" t="s">
         <v>168</v>
       </c>
@@ -5897,7 +5972,6 @@
       <c r="C100" t="s">
         <v>8</v>
       </c>
-      <c r="D100" s="2"/>
       <c r="E100" t="s">
         <v>173</v>
       </c>
@@ -6071,7 +6145,6 @@
       <c r="C114" t="s">
         <v>8</v>
       </c>
-      <c r="D114" s="2"/>
       <c r="E114" t="s">
         <v>201</v>
       </c>
@@ -6097,7 +6170,6 @@
       <c r="C116" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D116" s="2"/>
       <c r="E116" s="9"/>
     </row>
     <row r="117" spans="1:3">
@@ -6143,7 +6215,6 @@
       <c r="C120" t="s">
         <v>8</v>
       </c>
-      <c r="D120" s="2"/>
       <c r="E120" t="s">
         <v>213</v>
       </c>
@@ -6219,7 +6290,6 @@
       <c r="C126" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D126" s="2"/>
       <c r="E126" s="9"/>
     </row>
     <row r="127" spans="1:3">
@@ -6314,7 +6384,7 @@
       </c>
       <c r="D134" s="11"/>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" ht="14.25" spans="1:6">
       <c r="A135" t="s">
         <v>244</v>
       </c>
@@ -6478,7 +6548,6 @@
       <c r="C148" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="D148" s="2"/>
       <c r="E148" s="9"/>
     </row>
     <row r="149" spans="1:3">
@@ -6502,7 +6571,6 @@
       <c r="C150" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="D150" s="2"/>
       <c r="E150" s="9"/>
     </row>
     <row r="151" spans="1:5">
@@ -6515,7 +6583,6 @@
       <c r="C151" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="D151" s="2"/>
       <c r="E151" s="9"/>
     </row>
     <row r="152" spans="1:3">
@@ -6769,7 +6836,6 @@
       <c r="C169" t="s">
         <v>255</v>
       </c>
-      <c r="D169" s="2"/>
       <c r="E169" t="s">
         <v>300</v>
       </c>
@@ -8087,7 +8153,6 @@
       <c r="C260" t="s">
         <v>255</v>
       </c>
-      <c r="D260" s="2"/>
       <c r="F260" s="3" t="s">
         <v>427</v>
       </c>
@@ -8754,7 +8819,6 @@
       <c r="C317" t="s">
         <v>255</v>
       </c>
-      <c r="D317" s="2"/>
       <c r="E317" t="s">
         <v>518</v>
       </c>
@@ -9532,7 +9596,6 @@
       <c r="C384" t="s">
         <v>255</v>
       </c>
-      <c r="D384" s="2"/>
       <c r="E384" t="s">
         <v>641</v>
       </c>
@@ -9773,7 +9836,6 @@
       <c r="C405" t="s">
         <v>255</v>
       </c>
-      <c r="D405" s="2"/>
       <c r="E405" t="s">
         <v>669</v>
       </c>
@@ -9824,7 +9886,6 @@
       <c r="C409" t="s">
         <v>255</v>
       </c>
-      <c r="D409" s="2"/>
       <c r="E409" t="s">
         <v>675</v>
       </c>
@@ -9986,7 +10047,6 @@
       <c r="C423" t="s">
         <v>255</v>
       </c>
-      <c r="D423" s="2"/>
       <c r="E423" t="s">
         <v>700</v>
       </c>
@@ -10073,7 +10133,6 @@
       <c r="C430" t="s">
         <v>255</v>
       </c>
-      <c r="D430" s="2"/>
       <c r="E430" t="s">
         <v>716</v>
       </c>
@@ -10519,7 +10578,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="470" ht="15.6" spans="1:3">
+    <row r="470" ht="14.25" spans="1:3">
       <c r="A470" t="s">
         <v>509</v>
       </c>
@@ -10634,7 +10693,6 @@
       <c r="C479" t="s">
         <v>255</v>
       </c>
-      <c r="D479" s="2"/>
       <c r="E479" t="s">
         <v>799</v>
       </c>
@@ -10903,7 +10961,6 @@
       <c r="C502" t="s">
         <v>255</v>
       </c>
-      <c r="D502" s="2"/>
       <c r="F502" s="9">
         <v>2536595683</v>
       </c>
@@ -11167,7 +11224,6 @@
       <c r="C525" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="D525" s="2"/>
       <c r="E525" s="9"/>
     </row>
     <row r="526" spans="1:3">
@@ -11366,7 +11422,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="543" ht="15" spans="1:5">
+    <row r="543" spans="1:5">
       <c r="A543" s="17" t="s">
         <v>891</v>
       </c>
@@ -11376,7 +11432,6 @@
       <c r="C543" t="s">
         <v>255</v>
       </c>
-      <c r="D543" s="2"/>
       <c r="E543" t="s">
         <v>893</v>
       </c>
@@ -11514,7 +11569,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="556" ht="15.6" spans="1:3">
+    <row r="556" ht="14.25" spans="1:3">
       <c r="A556" s="12" t="s">
         <v>913</v>
       </c>
@@ -11819,7 +11874,6 @@
       <c r="C581" t="s">
         <v>255</v>
       </c>
-      <c r="D581" s="2"/>
       <c r="E581" t="s">
         <v>962</v>
       </c>
@@ -12463,7 +12517,6 @@
       <c r="C637" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="D637" s="2"/>
       <c r="F637" s="9" t="s">
         <v>1057</v>
       </c>
@@ -12566,7 +12619,6 @@
       <c r="C646" t="s">
         <v>255</v>
       </c>
-      <c r="D646" s="2"/>
       <c r="E646" t="s">
         <v>1067</v>
       </c>
@@ -12704,106 +12756,252 @@
       </c>
     </row>
     <row r="659" spans="1:4">
-      <c r="A659" s="10"/>
-      <c r="C659" s="10"/>
+      <c r="A659" s="10" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B659" t="s">
+        <v>731</v>
+      </c>
+      <c r="C659" t="s">
+        <v>255</v>
+      </c>
       <c r="D659" s="11"/>
     </row>
     <row r="660" spans="1:3">
-      <c r="A660" s="10"/>
-      <c r="B660" s="10"/>
-      <c r="C660" s="10"/>
+      <c r="A660" s="10" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B660" s="10" t="s">
+        <v>557</v>
+      </c>
+      <c r="C660" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="661" spans="1:3">
-      <c r="A661" s="10"/>
-      <c r="B661" s="10"/>
-      <c r="C661" s="10"/>
+      <c r="A661" s="10" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B661" s="10" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C661" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="662" spans="1:4">
-      <c r="A662" s="10"/>
-      <c r="B662" s="10"/>
-      <c r="C662" s="10"/>
+      <c r="A662" s="10" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B662" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="C662" t="s">
+        <v>255</v>
+      </c>
       <c r="D662" s="11"/>
     </row>
     <row r="663" spans="1:3">
-      <c r="A663" s="10"/>
-      <c r="C663" s="10"/>
+      <c r="A663" s="10" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B663" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C663" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="664" spans="1:4">
-      <c r="A664" s="10"/>
-      <c r="C664" s="10"/>
+      <c r="A664" s="10" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B664" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C664" t="s">
+        <v>8</v>
+      </c>
       <c r="D664" s="11"/>
     </row>
     <row r="665" spans="1:3">
-      <c r="A665" s="10"/>
-      <c r="B665" s="10"/>
-      <c r="C665" s="10"/>
-    </row>
-    <row r="666" spans="2:3">
-      <c r="B666" s="10"/>
-      <c r="C666" s="10"/>
-    </row>
-    <row r="667" spans="3:3">
-      <c r="C667" s="10"/>
+      <c r="A665" s="10" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B665" s="10" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C665" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="666" spans="1:3">
+      <c r="A666" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B666" s="10" t="s">
+        <v>951</v>
+      </c>
+      <c r="C666" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="667" spans="1:3">
+      <c r="A667" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B667" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C667" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="668" spans="1:3">
-      <c r="A668" s="10"/>
-      <c r="C668" s="10"/>
+      <c r="A668" s="10" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B668" t="s">
+        <v>319</v>
+      </c>
+      <c r="C668" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="669" spans="1:3">
-      <c r="A669" s="10"/>
-      <c r="C669" s="10"/>
+      <c r="A669" s="10" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B669" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C669" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="670" spans="1:3">
-      <c r="A670" s="10"/>
-      <c r="B670" s="10"/>
-      <c r="C670" s="10"/>
+      <c r="A670" s="10" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B670" s="10" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C670" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="671" spans="1:4">
-      <c r="A671" s="10"/>
-      <c r="C671" s="10"/>
+      <c r="A671" s="10" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B671" t="s">
+        <v>319</v>
+      </c>
+      <c r="C671" t="s">
+        <v>255</v>
+      </c>
       <c r="D671" s="11"/>
     </row>
     <row r="672" spans="1:3">
-      <c r="A672" s="10"/>
-      <c r="C672" s="10"/>
+      <c r="A672" s="10" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B672" t="s">
+        <v>658</v>
+      </c>
+      <c r="C672" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="673" spans="1:3">
-      <c r="A673" s="10"/>
-      <c r="C673" s="10"/>
+      <c r="A673" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="B673" t="s">
+        <v>319</v>
+      </c>
+      <c r="C673" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="674" spans="1:3">
-      <c r="A674" s="10"/>
-      <c r="B674" s="10"/>
-      <c r="C674" s="10"/>
-    </row>
-    <row r="675" spans="3:3">
-      <c r="C675" s="10"/>
+      <c r="A674" s="10" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B674" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="C674" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="675" spans="1:3">
+      <c r="A675" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B675" t="s">
+        <v>319</v>
+      </c>
+      <c r="C675" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="676" spans="1:3">
-      <c r="A676" s="10"/>
-      <c r="B676" s="10"/>
-      <c r="C676" s="10"/>
+      <c r="A676" s="10" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B676" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="C676" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="677" spans="1:4">
-      <c r="A677" s="10"/>
-      <c r="B677" s="10"/>
-      <c r="C677" s="10"/>
+      <c r="A677" s="10" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B677" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="C677" t="s">
+        <v>255</v>
+      </c>
       <c r="D677" s="11"/>
     </row>
     <row r="678" spans="1:4">
-      <c r="A678" s="10"/>
-      <c r="B678" s="10"/>
-      <c r="C678" s="10"/>
+      <c r="A678" s="10" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B678" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="C678" t="s">
+        <v>255</v>
+      </c>
       <c r="D678" s="11"/>
     </row>
     <row r="679" spans="1:3">
-      <c r="A679" s="10"/>
-      <c r="C679" s="10"/>
+      <c r="A679" s="10" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B679" t="s">
+        <v>731</v>
+      </c>
+      <c r="C679" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="680" spans="1:3">
-      <c r="A680" s="10"/>
-      <c r="B680" s="10"/>
-      <c r="C680" s="10"/>
+      <c r="A680" s="10" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B680" s="10" t="s">
+        <v>865</v>
+      </c>
+      <c r="C680" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="681" spans="1:4">
       <c r="A681" s="10"/>
@@ -13961,7 +14159,7 @@
       <c r="C915" s="10"/>
       <c r="D915" s="11"/>
     </row>
-    <row r="916" spans="1:4">
+    <row r="916" ht="14.25" spans="1:4">
       <c r="A916" s="29"/>
       <c r="B916" s="29"/>
       <c r="C916" s="10"/>
@@ -14756,8 +14954,8 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E658" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:E658">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E673" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:E673">
       <sortCondition ref="B1"/>
     </sortState>
     <extLst/>
@@ -14767,7 +14965,7 @@
     <sortCondition ref="B2:B658"/>
   </sortState>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C655 C656 C657 C658 C1:C635 C636:C645 C646:C650 C651:C654 C659:C1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C657 C658:C680 C681:C1048576">
       <formula1>"国语,日语,英语"</formula1>
     </dataValidation>
   </dataValidations>

--- a/scripts/music.xlsx
+++ b/scripts/music.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView windowWidth="14865" windowHeight="14055"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$680</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$728</definedName>
   </definedNames>
   <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2301" uniqueCount="1112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2493" uniqueCount="1172">
   <si>
     <t>歌名</t>
   </si>
@@ -3451,6 +3451,186 @@
   </si>
   <si>
     <t>卓文萱/曹格</t>
+  </si>
+  <si>
+    <t>表面的和平</t>
+  </si>
+  <si>
+    <t>new</t>
+  </si>
+  <si>
+    <t>人间惊鸿客</t>
+  </si>
+  <si>
+    <t>叶里</t>
+  </si>
+  <si>
+    <t>门</t>
+  </si>
+  <si>
+    <t>我们不是天使</t>
+  </si>
+  <si>
+    <t>For Blue</t>
+  </si>
+  <si>
+    <t>Love Me Love Me</t>
+  </si>
+  <si>
+    <t>光芒</t>
+  </si>
+  <si>
+    <t>冬季恋</t>
+  </si>
+  <si>
+    <t>银白色旋律</t>
+  </si>
+  <si>
+    <t>小宇</t>
+  </si>
+  <si>
+    <t>sweet trap</t>
+  </si>
+  <si>
+    <t>夏之回忆</t>
+  </si>
+  <si>
+    <t>李艺彤</t>
+  </si>
+  <si>
+    <t>打错了</t>
+  </si>
+  <si>
+    <t>moonlight</t>
+  </si>
+  <si>
+    <t>坐标121E 31N</t>
+  </si>
+  <si>
+    <t>升温</t>
+  </si>
+  <si>
+    <t>Lost</t>
+  </si>
+  <si>
+    <t>预言</t>
+  </si>
+  <si>
+    <t>花之祭</t>
+  </si>
+  <si>
+    <t>Sing Together</t>
+  </si>
+  <si>
+    <t>Forever XLVIII</t>
+  </si>
+  <si>
+    <t>Daisy Crown</t>
+  </si>
+  <si>
+    <t>芜桃</t>
+  </si>
+  <si>
+    <t>临兵斗者皆阵列在前</t>
+  </si>
+  <si>
+    <t>Honor</t>
+  </si>
+  <si>
+    <t>青春的约定</t>
+  </si>
+  <si>
+    <t>公主披风</t>
+  </si>
+  <si>
+    <t>向日葵</t>
+  </si>
+  <si>
+    <t>少女的巴别塔</t>
+  </si>
+  <si>
+    <t>鱼仔</t>
+  </si>
+  <si>
+    <t>未来会来</t>
+  </si>
+  <si>
+    <t>星炬不熄</t>
+  </si>
+  <si>
+    <t>飞行雪绒</t>
+  </si>
+  <si>
+    <t>蠢货</t>
+  </si>
+  <si>
+    <t>喻言</t>
+  </si>
+  <si>
+    <t>空白格</t>
+  </si>
+  <si>
+    <t>我爱洗澡</t>
+  </si>
+  <si>
+    <t>范晓萱</t>
+  </si>
+  <si>
+    <t>左手右手</t>
+  </si>
+  <si>
+    <t>童年</t>
+  </si>
+  <si>
+    <t>罗大佑</t>
+  </si>
+  <si>
+    <t>踏浪</t>
+  </si>
+  <si>
+    <t>徐怀钰</t>
+  </si>
+  <si>
+    <t>Happy ReBirthday</t>
+  </si>
+  <si>
+    <t>吵架歌</t>
+  </si>
+  <si>
+    <t>思念</t>
+  </si>
+  <si>
+    <t>蝴蝶</t>
+  </si>
+  <si>
+    <t>陶喆</t>
+  </si>
+  <si>
+    <t>致明天</t>
+  </si>
+  <si>
+    <t>胆小鬼</t>
+  </si>
+  <si>
+    <t>梁咏琪</t>
+  </si>
+  <si>
+    <t>垃圾桶</t>
+  </si>
+  <si>
+    <t>爱你但说不出口</t>
+  </si>
+  <si>
+    <t>Karencici</t>
+  </si>
+  <si>
+    <t>Final奔向落日</t>
+  </si>
+  <si>
+    <t>B·rise梦之门</t>
+  </si>
+  <si>
+    <t>要你说爱我</t>
   </si>
 </sst>
 </file>
@@ -4700,7 +4880,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -4711,7 +4891,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:6">
       <c r="A3" s="8" t="s">
         <v>9</v>
       </c>
@@ -4722,7 +4902,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -4733,7 +4913,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -4747,7 +4927,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -4761,7 +4941,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:6">
       <c r="A7" s="8" t="s">
         <v>16</v>
       </c>
@@ -4773,7 +4953,7 @@
       </c>
       <c r="E7" s="9"/>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:6">
       <c r="A8" s="10" t="s">
         <v>17</v>
       </c>
@@ -4784,7 +4964,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:6">
       <c r="A9" s="10" t="s">
         <v>18</v>
       </c>
@@ -4796,7 +4976,7 @@
       </c>
       <c r="D9" s="11"/>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -4807,7 +4987,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -4818,7 +4998,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -4829,7 +5009,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -4840,7 +5020,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -4851,7 +5031,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -4862,7 +5042,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -4873,7 +5053,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -4884,7 +5064,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" ht="15" spans="1:3">
+    <row r="18" ht="15" spans="1:5">
       <c r="A18" s="12" t="s">
         <v>28</v>
       </c>
@@ -4895,7 +5075,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -4906,7 +5086,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -4917,7 +5097,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>31</v>
       </c>
@@ -4928,7 +5108,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>32</v>
       </c>
@@ -4939,7 +5119,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>33</v>
       </c>
@@ -4950,7 +5130,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:5">
       <c r="A24" s="8" t="s">
         <v>35</v>
       </c>
@@ -4961,7 +5141,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>37</v>
       </c>
@@ -4986,7 +5166,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -4997,7 +5177,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -5011,7 +5191,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
         <v>45</v>
       </c>
@@ -5034,7 +5214,7 @@
       </c>
       <c r="E30" s="9"/>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
         <v>49</v>
       </c>
@@ -5048,7 +5228,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
         <v>51</v>
       </c>
@@ -5062,7 +5242,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
         <v>52</v>
       </c>
@@ -5091,7 +5271,7 @@
       </c>
       <c r="E34" s="9"/>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
         <v>54</v>
       </c>
@@ -5105,7 +5285,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
         <v>56</v>
       </c>
@@ -5119,7 +5299,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
         <v>58</v>
       </c>
@@ -5147,7 +5327,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:5">
       <c r="A39" s="14" t="s">
         <v>63</v>
       </c>
@@ -5161,7 +5341,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
         <v>64</v>
       </c>
@@ -5175,7 +5355,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
         <v>66</v>
       </c>
@@ -5189,7 +5369,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
         <v>68</v>
       </c>
@@ -5203,7 +5383,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:5">
       <c r="A43" t="s">
         <v>69</v>
       </c>
@@ -5214,7 +5394,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
         <v>71</v>
       </c>
@@ -5225,7 +5405,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:5">
       <c r="A45" t="s">
         <v>73</v>
       </c>
@@ -5250,7 +5430,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:5">
       <c r="A47" s="10" t="s">
         <v>78</v>
       </c>
@@ -5262,7 +5442,7 @@
       </c>
       <c r="D47" s="11"/>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:5">
       <c r="A48" s="10" t="s">
         <v>80</v>
       </c>
@@ -5273,7 +5453,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:5">
       <c r="A49" s="10" t="s">
         <v>82</v>
       </c>
@@ -5285,7 +5465,7 @@
       </c>
       <c r="D49" s="11"/>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:5">
       <c r="A50" t="s">
         <v>84</v>
       </c>
@@ -5296,7 +5476,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:5">
       <c r="A51" s="10" t="s">
         <v>86</v>
       </c>
@@ -5307,7 +5487,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:5">
       <c r="A52" t="s">
         <v>88</v>
       </c>
@@ -5332,7 +5512,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:5">
       <c r="A54" t="s">
         <v>93</v>
       </c>
@@ -5343,7 +5523,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:5">
       <c r="A55" t="s">
         <v>94</v>
       </c>
@@ -5354,7 +5534,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:5">
       <c r="A56" t="s">
         <v>96</v>
       </c>
@@ -5379,7 +5559,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:5">
       <c r="A58" t="s">
         <v>99</v>
       </c>
@@ -5390,7 +5570,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:5">
       <c r="A59" t="s">
         <v>101</v>
       </c>
@@ -5401,7 +5581,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:5">
       <c r="A60" t="s">
         <v>103</v>
       </c>
@@ -5429,7 +5609,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:5">
       <c r="A62" t="s">
         <v>108</v>
       </c>
@@ -5440,7 +5620,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:5">
       <c r="A63" t="s">
         <v>110</v>
       </c>
@@ -5465,7 +5645,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:5">
       <c r="A65" s="10" t="s">
         <v>115</v>
       </c>
@@ -5476,7 +5656,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:5">
       <c r="A66" t="s">
         <v>117</v>
       </c>
@@ -5487,7 +5667,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:5">
       <c r="A67" t="s">
         <v>119</v>
       </c>
@@ -5510,7 +5690,7 @@
       </c>
       <c r="E68" s="9"/>
     </row>
-    <row r="69" spans="1:4">
+    <row r="69" spans="1:5">
       <c r="A69" t="s">
         <v>122</v>
       </c>
@@ -5524,7 +5704,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="70" spans="1:4">
+    <row r="70" spans="1:5">
       <c r="A70" t="s">
         <v>124</v>
       </c>
@@ -5606,7 +5786,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
+    <row r="75" spans="1:5">
       <c r="A75" t="s">
         <v>133</v>
       </c>
@@ -5620,7 +5800,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
+    <row r="76" spans="1:5">
       <c r="A76" t="s">
         <v>134</v>
       </c>
@@ -5717,7 +5897,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:5">
       <c r="A82" t="s">
         <v>144</v>
       </c>
@@ -5748,7 +5928,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="84" spans="1:4">
+    <row r="84" spans="1:5">
       <c r="A84" t="s">
         <v>147</v>
       </c>
@@ -5762,7 +5942,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:5">
       <c r="A85" t="s">
         <v>148</v>
       </c>
@@ -5776,7 +5956,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
+    <row r="86" spans="1:5">
       <c r="A86" t="s">
         <v>149</v>
       </c>
@@ -5805,7 +5985,7 @@
       </c>
       <c r="E87" s="9"/>
     </row>
-    <row r="88" spans="1:4">
+    <row r="88" spans="1:5">
       <c r="A88" t="s">
         <v>151</v>
       </c>
@@ -5834,7 +6014,7 @@
       </c>
       <c r="E89" s="9"/>
     </row>
-    <row r="90" spans="1:4">
+    <row r="90" spans="1:5">
       <c r="A90" t="s">
         <v>153</v>
       </c>
@@ -5848,7 +6028,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="91" spans="1:4">
+    <row r="91" spans="1:5">
       <c r="A91" t="s">
         <v>154</v>
       </c>
@@ -5862,7 +6042,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="92" spans="1:4">
+    <row r="92" spans="1:5">
       <c r="A92" t="s">
         <v>155</v>
       </c>
@@ -5876,7 +6056,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:5">
       <c r="A93" s="8" t="s">
         <v>156</v>
       </c>
@@ -5887,7 +6067,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:5">
       <c r="A94" t="s">
         <v>158</v>
       </c>
@@ -5898,7 +6078,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:5">
       <c r="A95" t="s">
         <v>160</v>
       </c>
@@ -5909,7 +6089,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:5">
       <c r="A96" t="s">
         <v>161</v>
       </c>
@@ -5937,7 +6117,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:6">
       <c r="A98" t="s">
         <v>166</v>
       </c>
@@ -5951,7 +6131,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:6">
       <c r="A99" t="s">
         <v>169</v>
       </c>
@@ -5962,7 +6142,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:6">
       <c r="A100" t="s">
         <v>171</v>
       </c>
@@ -5976,7 +6156,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:6">
       <c r="A101" t="s">
         <v>174</v>
       </c>
@@ -5987,7 +6167,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" spans="1:6">
       <c r="A102" t="s">
         <v>176</v>
       </c>
@@ -5998,7 +6178,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
+    <row r="103" spans="1:6">
       <c r="A103" t="s">
         <v>178</v>
       </c>
@@ -6012,7 +6192,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:6">
       <c r="A104" t="s">
         <v>180</v>
       </c>
@@ -6029,7 +6209,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
+    <row r="105" spans="1:6">
       <c r="A105" t="s">
         <v>182</v>
       </c>
@@ -6043,7 +6223,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
+    <row r="106" spans="1:6">
       <c r="A106" t="s">
         <v>183</v>
       </c>
@@ -6057,7 +6237,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="107" spans="1:3">
+    <row r="107" spans="1:6">
       <c r="A107" t="s">
         <v>185</v>
       </c>
@@ -6068,7 +6248,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="108" spans="1:3">
+    <row r="108" spans="1:6">
       <c r="A108" t="s">
         <v>187</v>
       </c>
@@ -6079,7 +6259,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:3">
+    <row r="109" spans="1:6">
       <c r="A109" t="s">
         <v>189</v>
       </c>
@@ -6090,7 +6270,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="110" spans="1:3">
+    <row r="110" spans="1:6">
       <c r="A110" t="s">
         <v>191</v>
       </c>
@@ -6101,7 +6281,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="111" spans="1:3">
+    <row r="111" spans="1:6">
       <c r="A111" t="s">
         <v>193</v>
       </c>
@@ -6112,7 +6292,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="112" spans="1:3">
+    <row r="112" spans="1:6">
       <c r="A112" t="s">
         <v>195</v>
       </c>
@@ -6123,7 +6303,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="113" spans="1:4">
+    <row r="113" spans="1:5">
       <c r="A113" s="10" t="s">
         <v>197</v>
       </c>
@@ -6161,7 +6341,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
+    <row r="116" spans="1:5">
       <c r="A116" t="s">
         <v>204</v>
       </c>
@@ -6184,7 +6364,7 @@
       </c>
       <c r="E117" s="9"/>
     </row>
-    <row r="118" spans="1:3">
+    <row r="118" spans="1:5">
       <c r="A118" t="s">
         <v>208</v>
       </c>
@@ -6195,7 +6375,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
+    <row r="119" spans="1:5">
       <c r="A119" s="10" t="s">
         <v>210</v>
       </c>
@@ -6206,7 +6386,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
+    <row r="120" spans="1:5">
       <c r="A120" t="s">
         <v>212</v>
       </c>
@@ -6231,7 +6411,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
+    <row r="122" spans="1:5">
       <c r="A122" t="s">
         <v>216</v>
       </c>
@@ -6256,7 +6436,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="124" spans="1:3">
+    <row r="124" spans="1:5">
       <c r="A124" t="s">
         <v>221</v>
       </c>
@@ -6281,7 +6461,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="126" spans="1:3">
+    <row r="126" spans="1:5">
       <c r="A126" t="s">
         <v>226</v>
       </c>
@@ -6304,7 +6484,7 @@
       </c>
       <c r="E127" s="9"/>
     </row>
-    <row r="128" spans="1:3">
+    <row r="128" spans="1:5">
       <c r="A128" t="s">
         <v>230</v>
       </c>
@@ -6315,7 +6495,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="129" spans="1:3">
+    <row r="129" spans="1:6">
       <c r="A129" t="s">
         <v>232</v>
       </c>
@@ -6326,7 +6506,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="130" spans="1:3">
+    <row r="130" spans="1:6">
       <c r="A130" t="s">
         <v>234</v>
       </c>
@@ -6337,7 +6517,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="131" spans="1:3">
+    <row r="131" spans="1:6">
       <c r="A131" t="s">
         <v>235</v>
       </c>
@@ -6348,7 +6528,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="132" spans="1:3">
+    <row r="132" spans="1:6">
       <c r="A132" s="10" t="s">
         <v>236</v>
       </c>
@@ -6359,7 +6539,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="133" spans="1:5">
+    <row r="133" spans="1:6">
       <c r="A133" s="8" t="s">
         <v>238</v>
       </c>
@@ -6373,7 +6553,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="134" spans="1:3">
+    <row r="134" spans="1:6">
       <c r="A134" s="10" t="s">
         <v>241</v>
       </c>
@@ -6384,7 +6564,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="135" spans="1:4">
+    <row r="135" spans="1:6">
       <c r="A135" s="10" t="s">
         <v>243</v>
       </c>
@@ -6410,7 +6590,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="137" spans="1:3">
+    <row r="137" spans="1:6">
       <c r="A137" t="s">
         <v>249</v>
       </c>
@@ -6421,7 +6601,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="138" spans="1:5">
+    <row r="138" spans="1:6">
       <c r="A138" t="s">
         <v>251</v>
       </c>
@@ -6435,7 +6615,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="139" spans="1:3">
+    <row r="139" spans="1:6">
       <c r="A139" t="s">
         <v>254</v>
       </c>
@@ -6446,7 +6626,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="140" spans="1:3">
+    <row r="140" spans="1:6">
       <c r="A140" s="10" t="s">
         <v>256</v>
       </c>
@@ -6457,7 +6637,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="141" spans="1:4">
+    <row r="141" spans="1:6">
       <c r="A141" s="10" t="s">
         <v>259</v>
       </c>
@@ -6469,7 +6649,7 @@
       </c>
       <c r="D141" s="11"/>
     </row>
-    <row r="142" spans="1:3">
+    <row r="142" spans="1:6">
       <c r="A142" t="s">
         <v>260</v>
       </c>
@@ -6480,7 +6660,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="143" spans="1:4">
+    <row r="143" spans="1:6">
       <c r="A143" t="s">
         <v>262</v>
       </c>
@@ -6494,7 +6674,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="144" spans="1:4">
+    <row r="144" spans="1:6">
       <c r="A144" s="10" t="s">
         <v>265</v>
       </c>
@@ -6506,7 +6686,7 @@
       </c>
       <c r="D144" s="11"/>
     </row>
-    <row r="145" spans="1:3">
+    <row r="145" spans="1:5">
       <c r="A145" t="s">
         <v>266</v>
       </c>
@@ -6517,7 +6697,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="146" spans="1:3">
+    <row r="146" spans="1:5">
       <c r="A146" t="s">
         <v>268</v>
       </c>
@@ -6528,7 +6708,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="147" spans="1:3">
+    <row r="147" spans="1:5">
       <c r="A147" t="s">
         <v>269</v>
       </c>
@@ -6539,7 +6719,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="148" spans="1:4">
+    <row r="148" spans="1:5">
       <c r="A148" s="10" t="s">
         <v>270</v>
       </c>
@@ -6551,7 +6731,7 @@
       </c>
       <c r="D148" s="11"/>
     </row>
-    <row r="149" spans="1:3">
+    <row r="149" spans="1:5">
       <c r="A149" t="s">
         <v>271</v>
       </c>
@@ -6562,7 +6742,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="150" spans="1:3">
+    <row r="150" spans="1:5">
       <c r="A150" t="s">
         <v>273</v>
       </c>
@@ -6585,7 +6765,7 @@
       </c>
       <c r="E151" s="9"/>
     </row>
-    <row r="152" spans="1:3">
+    <row r="152" spans="1:5">
       <c r="A152" t="s">
         <v>277</v>
       </c>
@@ -6620,7 +6800,7 @@
       </c>
       <c r="E154" s="9"/>
     </row>
-    <row r="155" spans="1:3">
+    <row r="155" spans="1:5">
       <c r="A155" t="s">
         <v>280</v>
       </c>
@@ -6631,7 +6811,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="156" spans="1:3">
+    <row r="156" spans="1:5">
       <c r="A156" t="s">
         <v>281</v>
       </c>
@@ -6642,7 +6822,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="157" spans="1:3">
+    <row r="157" spans="1:5">
       <c r="A157" t="s">
         <v>282</v>
       </c>
@@ -6653,7 +6833,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="158" spans="1:4">
+    <row r="158" spans="1:5">
       <c r="A158" s="8" t="s">
         <v>284</v>
       </c>
@@ -6667,7 +6847,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="159" spans="1:4">
+    <row r="159" spans="1:5">
       <c r="A159" s="8" t="s">
         <v>286</v>
       </c>
@@ -6681,7 +6861,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="160" spans="1:4">
+    <row r="160" spans="1:5">
       <c r="A160" t="s">
         <v>287</v>
       </c>
@@ -6729,7 +6909,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="163" spans="1:4">
+    <row r="163" spans="1:5">
       <c r="A163" t="s">
         <v>292</v>
       </c>
@@ -6743,7 +6923,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="164" spans="1:4">
+    <row r="164" spans="1:5">
       <c r="A164" s="8" t="s">
         <v>293</v>
       </c>
@@ -6757,7 +6937,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="165" spans="1:4">
+    <row r="165" spans="1:5">
       <c r="A165" s="8" t="s">
         <v>294</v>
       </c>
@@ -6771,7 +6951,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="166" spans="1:4">
+    <row r="166" spans="1:5">
       <c r="A166" t="s">
         <v>295</v>
       </c>
@@ -6802,7 +6982,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="168" spans="1:4">
+    <row r="168" spans="1:5">
       <c r="A168" s="8" t="s">
         <v>298</v>
       </c>
@@ -6816,7 +6996,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="169" spans="1:4">
+    <row r="169" spans="1:5">
       <c r="A169" s="8" t="s">
         <v>299</v>
       </c>
@@ -6847,7 +7027,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="171" spans="1:4">
+    <row r="171" spans="1:5">
       <c r="A171" s="10" t="s">
         <v>302</v>
       </c>
@@ -6875,7 +7055,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="173" spans="1:3">
+    <row r="173" spans="1:5">
       <c r="A173" t="s">
         <v>306</v>
       </c>
@@ -6886,7 +7066,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="174" spans="1:3">
+    <row r="174" spans="1:5">
       <c r="A174" t="s">
         <v>308</v>
       </c>
@@ -6897,7 +7077,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="175" spans="1:3">
+    <row r="175" spans="1:5">
       <c r="A175" t="s">
         <v>310</v>
       </c>
@@ -6908,7 +7088,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="176" spans="1:3">
+    <row r="176" spans="1:5">
       <c r="A176" t="s">
         <v>312</v>
       </c>
@@ -6919,7 +7099,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="177" spans="1:3">
+    <row r="177" spans="1:5">
       <c r="A177" t="s">
         <v>314</v>
       </c>
@@ -6930,7 +7110,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="178" spans="1:3">
+    <row r="178" spans="1:5">
       <c r="A178" t="s">
         <v>315</v>
       </c>
@@ -6941,7 +7121,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="179" spans="1:3">
+    <row r="179" spans="1:5">
       <c r="A179" t="s">
         <v>317</v>
       </c>
@@ -6952,7 +7132,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="180" spans="1:4">
+    <row r="180" spans="1:5">
       <c r="A180" s="10" t="s">
         <v>318</v>
       </c>
@@ -6966,7 +7146,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="181" spans="1:4">
+    <row r="181" spans="1:5">
       <c r="A181" s="10" t="s">
         <v>320</v>
       </c>
@@ -6980,7 +7160,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="182" spans="1:3">
+    <row r="182" spans="1:5">
       <c r="A182" t="s">
         <v>321</v>
       </c>
@@ -7008,7 +7188,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="184" spans="1:4">
+    <row r="184" spans="1:5">
       <c r="A184" t="s">
         <v>326</v>
       </c>
@@ -7037,7 +7217,7 @@
       </c>
       <c r="E185" s="9"/>
     </row>
-    <row r="186" spans="1:4">
+    <row r="186" spans="1:5">
       <c r="A186" t="s">
         <v>328</v>
       </c>
@@ -7051,7 +7231,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="187" spans="1:4">
+    <row r="187" spans="1:5">
       <c r="A187" t="s">
         <v>329</v>
       </c>
@@ -7065,7 +7245,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="188" spans="1:4">
+    <row r="188" spans="1:5">
       <c r="A188" t="s">
         <v>330</v>
       </c>
@@ -7079,7 +7259,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="189" spans="1:4">
+    <row r="189" spans="1:5">
       <c r="A189" t="s">
         <v>331</v>
       </c>
@@ -7093,7 +7273,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="190" spans="1:4">
+    <row r="190" spans="1:5">
       <c r="A190" t="s">
         <v>332</v>
       </c>
@@ -7141,7 +7321,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="193" spans="1:4">
+    <row r="193" spans="1:6">
       <c r="A193" t="s">
         <v>337</v>
       </c>
@@ -7175,7 +7355,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="195" spans="1:4">
+    <row r="195" spans="1:6">
       <c r="A195" t="s">
         <v>341</v>
       </c>
@@ -7189,7 +7369,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="196" spans="1:4">
+    <row r="196" spans="1:6">
       <c r="A196" t="s">
         <v>342</v>
       </c>
@@ -7203,7 +7383,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="197" spans="1:4">
+    <row r="197" spans="1:6">
       <c r="A197" t="s">
         <v>343</v>
       </c>
@@ -7217,7 +7397,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="198" spans="1:4">
+    <row r="198" spans="1:6">
       <c r="A198" t="s">
         <v>344</v>
       </c>
@@ -7231,7 +7411,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="199" spans="1:5">
+    <row r="199" spans="1:6">
       <c r="A199" s="8" t="s">
         <v>345</v>
       </c>
@@ -7246,7 +7426,7 @@
       </c>
       <c r="E199" s="9"/>
     </row>
-    <row r="200" spans="1:4">
+    <row r="200" spans="1:6">
       <c r="A200" s="10" t="s">
         <v>346</v>
       </c>
@@ -7260,7 +7440,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="201" spans="1:5">
+    <row r="201" spans="1:6">
       <c r="A201" t="s">
         <v>347</v>
       </c>
@@ -7277,7 +7457,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="202" spans="1:4">
+    <row r="202" spans="1:6">
       <c r="A202" t="s">
         <v>349</v>
       </c>
@@ -7291,7 +7471,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="203" spans="1:4">
+    <row r="203" spans="1:6">
       <c r="A203" t="s">
         <v>350</v>
       </c>
@@ -7305,7 +7485,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="204" spans="1:4">
+    <row r="204" spans="1:6">
       <c r="A204" t="s">
         <v>351</v>
       </c>
@@ -7319,7 +7499,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="205" spans="1:4">
+    <row r="205" spans="1:6">
       <c r="A205" t="s">
         <v>352</v>
       </c>
@@ -7333,7 +7513,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="206" spans="1:5">
+    <row r="206" spans="1:6">
       <c r="A206" t="s">
         <v>353</v>
       </c>
@@ -7350,7 +7530,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="207" spans="1:4">
+    <row r="207" spans="1:6">
       <c r="A207" t="s">
         <v>355</v>
       </c>
@@ -7364,7 +7544,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="208" spans="1:4">
+    <row r="208" spans="1:6">
       <c r="A208" t="s">
         <v>356</v>
       </c>
@@ -7429,7 +7609,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="212" spans="1:4">
+    <row r="212" spans="1:5">
       <c r="A212" t="s">
         <v>363</v>
       </c>
@@ -7443,7 +7623,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="213" spans="1:4">
+    <row r="213" spans="1:5">
       <c r="A213" s="8" t="s">
         <v>364</v>
       </c>
@@ -7542,7 +7722,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="219" spans="1:4">
+    <row r="219" spans="1:5">
       <c r="A219" t="s">
         <v>375</v>
       </c>
@@ -7556,7 +7736,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="220" spans="1:4">
+    <row r="220" spans="1:5">
       <c r="A220" t="s">
         <v>376</v>
       </c>
@@ -7600,7 +7780,7 @@
       </c>
       <c r="E222" s="9"/>
     </row>
-    <row r="223" spans="1:4">
+    <row r="223" spans="1:5">
       <c r="A223" t="s">
         <v>379</v>
       </c>
@@ -7614,7 +7794,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="224" spans="1:4">
+    <row r="224" spans="1:5">
       <c r="A224" s="8" t="s">
         <v>380</v>
       </c>
@@ -7648,7 +7828,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="226" spans="1:4">
+    <row r="226" spans="1:6">
       <c r="A226" t="s">
         <v>384</v>
       </c>
@@ -7662,7 +7842,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="227" spans="1:5">
+    <row r="227" spans="1:6">
       <c r="A227" t="s">
         <v>385</v>
       </c>
@@ -7679,7 +7859,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="228" spans="1:4">
+    <row r="228" spans="1:6">
       <c r="A228" t="s">
         <v>387</v>
       </c>
@@ -7693,7 +7873,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="229" spans="1:4">
+    <row r="229" spans="1:6">
       <c r="A229" t="s">
         <v>388</v>
       </c>
@@ -7707,7 +7887,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="230" spans="1:4">
+    <row r="230" spans="1:6">
       <c r="A230" t="s">
         <v>389</v>
       </c>
@@ -7721,7 +7901,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="231" spans="1:4">
+    <row r="231" spans="1:6">
       <c r="A231" t="s">
         <v>390</v>
       </c>
@@ -7735,7 +7915,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="232" spans="1:5">
+    <row r="232" spans="1:6">
       <c r="A232" s="8" t="s">
         <v>391</v>
       </c>
@@ -7750,7 +7930,7 @@
       </c>
       <c r="E232" s="9"/>
     </row>
-    <row r="233" spans="1:4">
+    <row r="233" spans="1:6">
       <c r="A233" t="s">
         <v>392</v>
       </c>
@@ -7764,7 +7944,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="234" spans="1:4">
+    <row r="234" spans="1:6">
       <c r="A234" t="s">
         <v>393</v>
       </c>
@@ -7778,7 +7958,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="235" spans="1:4">
+    <row r="235" spans="1:6">
       <c r="A235" t="s">
         <v>394</v>
       </c>
@@ -7792,7 +7972,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="236" spans="1:4">
+    <row r="236" spans="1:6">
       <c r="A236" t="s">
         <v>395</v>
       </c>
@@ -7806,7 +7986,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="237" spans="1:4">
+    <row r="237" spans="1:6">
       <c r="A237" t="s">
         <v>396</v>
       </c>
@@ -7820,7 +8000,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="238" spans="1:4">
+    <row r="238" spans="1:6">
       <c r="A238" t="s">
         <v>397</v>
       </c>
@@ -7834,7 +8014,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="239" spans="1:4">
+    <row r="239" spans="1:6">
       <c r="A239" t="s">
         <v>398</v>
       </c>
@@ -7848,7 +8028,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="240" spans="1:4">
+    <row r="240" spans="1:6">
       <c r="A240" t="s">
         <v>399</v>
       </c>
@@ -7862,7 +8042,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="241" spans="1:4">
+    <row r="241" spans="1:5">
       <c r="A241" t="s">
         <v>400</v>
       </c>
@@ -7876,7 +8056,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="242" spans="1:4">
+    <row r="242" spans="1:5">
       <c r="A242" s="8" t="s">
         <v>401</v>
       </c>
@@ -7890,7 +8070,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="243" spans="1:4">
+    <row r="243" spans="1:5">
       <c r="A243" t="s">
         <v>402</v>
       </c>
@@ -7904,7 +8084,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="244" spans="1:4">
+    <row r="244" spans="1:5">
       <c r="A244" t="s">
         <v>403</v>
       </c>
@@ -7933,7 +8113,7 @@
       </c>
       <c r="E245" s="9"/>
     </row>
-    <row r="246" spans="1:4">
+    <row r="246" spans="1:5">
       <c r="A246" t="s">
         <v>405</v>
       </c>
@@ -7994,7 +8174,7 @@
       </c>
       <c r="E249" s="9"/>
     </row>
-    <row r="250" spans="1:4">
+    <row r="250" spans="1:5">
       <c r="A250" t="s">
         <v>410</v>
       </c>
@@ -8025,7 +8205,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="252" spans="1:4">
+    <row r="252" spans="1:5">
       <c r="A252" t="s">
         <v>413</v>
       </c>
@@ -8103,7 +8283,7 @@
       </c>
       <c r="E256" s="9"/>
     </row>
-    <row r="257" spans="1:4">
+    <row r="257" spans="1:6">
       <c r="A257" s="10" t="s">
         <v>420</v>
       </c>
@@ -8117,7 +8297,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="258" spans="1:4">
+    <row r="258" spans="1:6">
       <c r="A258" s="10" t="s">
         <v>421</v>
       </c>
@@ -8131,7 +8311,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="259" spans="1:4">
+    <row r="259" spans="1:6">
       <c r="A259" s="10" t="s">
         <v>422</v>
       </c>
@@ -8143,7 +8323,7 @@
       </c>
       <c r="D259" s="11"/>
     </row>
-    <row r="260" spans="1:3">
+    <row r="260" spans="1:6">
       <c r="A260" s="10" t="s">
         <v>423</v>
       </c>
@@ -8154,7 +8334,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="261" spans="1:4">
+    <row r="261" spans="1:6">
       <c r="A261" s="10" t="s">
         <v>424</v>
       </c>
@@ -8166,7 +8346,7 @@
       </c>
       <c r="D261" s="11"/>
     </row>
-    <row r="262" spans="1:3">
+    <row r="262" spans="1:6">
       <c r="A262" s="10" t="s">
         <v>315</v>
       </c>
@@ -8177,7 +8357,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="263" spans="1:3">
+    <row r="263" spans="1:6">
       <c r="A263" s="10" t="s">
         <v>425</v>
       </c>
@@ -8188,7 +8368,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="264" spans="1:3">
+    <row r="264" spans="1:6">
       <c r="A264" t="s">
         <v>426</v>
       </c>
@@ -8199,7 +8379,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="265" spans="1:4">
+    <row r="265" spans="1:6">
       <c r="A265" s="10" t="s">
         <v>427</v>
       </c>
@@ -8211,7 +8391,7 @@
       </c>
       <c r="D265" s="11"/>
     </row>
-    <row r="266" spans="1:4">
+    <row r="266" spans="1:6">
       <c r="A266" t="s">
         <v>428</v>
       </c>
@@ -8225,7 +8405,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="267" spans="1:3">
+    <row r="267" spans="1:6">
       <c r="A267" t="s">
         <v>430</v>
       </c>
@@ -8236,7 +8416,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="268" spans="1:3">
+    <row r="268" spans="1:6">
       <c r="A268" t="s">
         <v>432</v>
       </c>
@@ -8247,7 +8427,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="269" spans="1:3">
+    <row r="269" spans="1:6">
       <c r="A269" t="s">
         <v>434</v>
       </c>
@@ -8272,7 +8452,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="271" spans="1:3">
+    <row r="271" spans="1:6">
       <c r="A271" t="s">
         <v>439</v>
       </c>
@@ -8283,7 +8463,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="272" spans="1:5">
+    <row r="272" spans="1:6">
       <c r="A272" t="s">
         <v>441</v>
       </c>
@@ -8297,7 +8477,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="273" spans="1:3">
+    <row r="273" spans="1:5">
       <c r="A273" t="s">
         <v>444</v>
       </c>
@@ -8322,7 +8502,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="275" spans="1:3">
+    <row r="275" spans="1:5">
       <c r="A275" t="s">
         <v>448</v>
       </c>
@@ -8333,7 +8513,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="276" spans="1:3">
+    <row r="276" spans="1:5">
       <c r="A276" t="s">
         <v>450</v>
       </c>
@@ -8344,7 +8524,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="277" spans="1:3">
+    <row r="277" spans="1:5">
       <c r="A277" t="s">
         <v>452</v>
       </c>
@@ -8355,7 +8535,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="278" spans="1:3">
+    <row r="278" spans="1:5">
       <c r="A278" s="10" t="s">
         <v>454</v>
       </c>
@@ -8366,7 +8546,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="279" spans="1:3">
+    <row r="279" spans="1:5">
       <c r="A279" t="s">
         <v>456</v>
       </c>
@@ -8391,7 +8571,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="281" spans="1:3">
+    <row r="281" spans="1:5">
       <c r="A281" t="s">
         <v>460</v>
       </c>
@@ -8402,7 +8582,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="282" spans="1:3">
+    <row r="282" spans="1:5">
       <c r="A282" t="s">
         <v>461</v>
       </c>
@@ -8425,7 +8605,7 @@
       </c>
       <c r="E283" s="9"/>
     </row>
-    <row r="284" spans="1:3">
+    <row r="284" spans="1:5">
       <c r="A284" t="s">
         <v>463</v>
       </c>
@@ -8450,7 +8630,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="286" spans="1:3">
+    <row r="286" spans="1:5">
       <c r="A286" t="s">
         <v>467</v>
       </c>
@@ -8461,7 +8641,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="287" spans="1:3">
+    <row r="287" spans="1:5">
       <c r="A287" t="s">
         <v>468</v>
       </c>
@@ -8486,7 +8666,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="289" spans="1:3">
+    <row r="289" spans="1:5">
       <c r="A289" t="s">
         <v>471</v>
       </c>
@@ -8497,7 +8677,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="290" spans="1:3">
+    <row r="290" spans="1:5">
       <c r="A290" s="8" t="s">
         <v>472</v>
       </c>
@@ -8522,7 +8702,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="292" spans="1:3">
+    <row r="292" spans="1:5">
       <c r="A292" t="s">
         <v>476</v>
       </c>
@@ -8533,7 +8713,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="293" spans="1:3">
+    <row r="293" spans="1:5">
       <c r="A293" t="s">
         <v>478</v>
       </c>
@@ -8544,7 +8724,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="294" spans="1:3">
+    <row r="294" spans="1:5">
       <c r="A294" t="s">
         <v>479</v>
       </c>
@@ -8555,7 +8735,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="295" spans="1:3">
+    <row r="295" spans="1:5">
       <c r="A295" t="s">
         <v>480</v>
       </c>
@@ -8566,7 +8746,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="296" spans="1:3">
+    <row r="296" spans="1:5">
       <c r="A296" t="s">
         <v>481</v>
       </c>
@@ -8577,7 +8757,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="297" spans="1:3">
+    <row r="297" spans="1:5">
       <c r="A297" t="s">
         <v>482</v>
       </c>
@@ -8588,7 +8768,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="298" spans="1:3">
+    <row r="298" spans="1:5">
       <c r="A298" t="s">
         <v>483</v>
       </c>
@@ -8599,7 +8779,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="299" spans="1:3">
+    <row r="299" spans="1:5">
       <c r="A299" t="s">
         <v>484</v>
       </c>
@@ -8622,7 +8802,7 @@
       </c>
       <c r="E300" s="9"/>
     </row>
-    <row r="301" spans="1:3">
+    <row r="301" spans="1:5">
       <c r="A301" t="s">
         <v>488</v>
       </c>
@@ -8633,7 +8813,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="302" spans="1:3">
+    <row r="302" spans="1:5">
       <c r="A302" t="s">
         <v>490</v>
       </c>
@@ -8644,7 +8824,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="303" spans="1:3">
+    <row r="303" spans="1:5">
       <c r="A303" t="s">
         <v>492</v>
       </c>
@@ -8669,7 +8849,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="305" spans="1:3">
+    <row r="305" spans="1:6">
       <c r="A305" t="s">
         <v>495</v>
       </c>
@@ -8680,7 +8860,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="306" spans="1:3">
+    <row r="306" spans="1:6">
       <c r="A306" t="s">
         <v>497</v>
       </c>
@@ -8691,7 +8871,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="307" spans="1:3">
+    <row r="307" spans="1:6">
       <c r="A307" t="s">
         <v>499</v>
       </c>
@@ -8702,7 +8882,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="308" spans="1:3">
+    <row r="308" spans="1:6">
       <c r="A308" t="s">
         <v>501</v>
       </c>
@@ -8713,7 +8893,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="309" spans="1:3">
+    <row r="309" spans="1:6">
       <c r="A309" s="8" t="s">
         <v>503</v>
       </c>
@@ -8724,7 +8904,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="310" spans="1:3">
+    <row r="310" spans="1:6">
       <c r="A310" t="s">
         <v>505</v>
       </c>
@@ -8735,7 +8915,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="311" spans="1:3">
+    <row r="311" spans="1:6">
       <c r="A311" t="s">
         <v>507</v>
       </c>
@@ -8760,7 +8940,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="313" spans="1:3">
+    <row r="313" spans="1:6">
       <c r="A313" t="s">
         <v>510</v>
       </c>
@@ -8771,7 +8951,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="314" spans="1:3">
+    <row r="314" spans="1:6">
       <c r="A314" t="s">
         <v>511</v>
       </c>
@@ -8782,7 +8962,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="315" spans="1:3">
+    <row r="315" spans="1:6">
       <c r="A315" t="s">
         <v>513</v>
       </c>
@@ -8793,7 +8973,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="316" spans="1:5">
+    <row r="316" spans="1:6">
       <c r="A316" t="s">
         <v>515</v>
       </c>
@@ -8807,7 +8987,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="317" spans="1:5">
+    <row r="317" spans="1:6">
       <c r="A317" s="8" t="s">
         <v>517</v>
       </c>
@@ -8819,7 +8999,7 @@
       </c>
       <c r="E317" s="9"/>
     </row>
-    <row r="318" spans="1:3">
+    <row r="318" spans="1:6">
       <c r="A318" t="s">
         <v>518</v>
       </c>
@@ -8830,7 +9010,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="319" spans="1:3">
+    <row r="319" spans="1:6">
       <c r="A319" t="s">
         <v>519</v>
       </c>
@@ -8841,7 +9021,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="320" spans="1:3">
+    <row r="320" spans="1:6">
       <c r="A320" t="s">
         <v>520</v>
       </c>
@@ -8852,7 +9032,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="321" spans="1:3">
+    <row r="321" spans="1:5">
       <c r="A321" t="s">
         <v>521</v>
       </c>
@@ -8877,7 +9057,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="323" spans="1:3">
+    <row r="323" spans="1:5">
       <c r="A323" t="s">
         <v>524</v>
       </c>
@@ -8888,7 +9068,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="324" spans="1:3">
+    <row r="324" spans="1:5">
       <c r="A324" t="s">
         <v>525</v>
       </c>
@@ -8913,7 +9093,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="326" spans="1:3">
+    <row r="326" spans="1:5">
       <c r="A326" t="s">
         <v>528</v>
       </c>
@@ -8924,7 +9104,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="327" spans="1:3">
+    <row r="327" spans="1:5">
       <c r="A327" t="s">
         <v>529</v>
       </c>
@@ -8949,7 +9129,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="329" spans="1:3">
+    <row r="329" spans="1:5">
       <c r="A329" s="10" t="s">
         <v>532</v>
       </c>
@@ -8960,7 +9140,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="330" spans="1:3">
+    <row r="330" spans="1:5">
       <c r="A330" t="s">
         <v>533</v>
       </c>
@@ -8971,7 +9151,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="331" spans="1:3">
+    <row r="331" spans="1:5">
       <c r="A331" t="s">
         <v>535</v>
       </c>
@@ -8982,7 +9162,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="332" spans="1:3">
+    <row r="332" spans="1:5">
       <c r="A332" t="s">
         <v>536</v>
       </c>
@@ -8993,7 +9173,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="333" spans="1:3">
+    <row r="333" spans="1:5">
       <c r="A333" t="s">
         <v>538</v>
       </c>
@@ -9018,7 +9198,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="335" spans="1:3">
+    <row r="335" spans="1:5">
       <c r="A335" t="s">
         <v>543</v>
       </c>
@@ -9043,7 +9223,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="337" spans="1:3">
+    <row r="337" spans="1:5">
       <c r="A337" t="s">
         <v>547</v>
       </c>
@@ -9054,7 +9234,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="338" spans="1:3">
+    <row r="338" spans="1:5">
       <c r="A338" t="s">
         <v>548</v>
       </c>
@@ -9065,7 +9245,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="339" spans="1:3">
+    <row r="339" spans="1:5">
       <c r="A339" t="s">
         <v>549</v>
       </c>
@@ -9076,7 +9256,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="340" spans="1:3">
+    <row r="340" spans="1:5">
       <c r="A340" t="s">
         <v>551</v>
       </c>
@@ -9087,7 +9267,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="341" spans="1:3">
+    <row r="341" spans="1:5">
       <c r="A341" t="s">
         <v>553</v>
       </c>
@@ -9098,7 +9278,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="342" spans="1:3">
+    <row r="342" spans="1:5">
       <c r="A342" t="s">
         <v>554</v>
       </c>
@@ -9135,7 +9315,7 @@
       </c>
       <c r="E344" s="9"/>
     </row>
-    <row r="345" spans="1:3">
+    <row r="345" spans="1:5">
       <c r="A345" t="s">
         <v>558</v>
       </c>
@@ -9146,7 +9326,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="346" spans="1:3">
+    <row r="346" spans="1:5">
       <c r="A346" t="s">
         <v>559</v>
       </c>
@@ -9157,7 +9337,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="347" spans="1:3">
+    <row r="347" spans="1:5">
       <c r="A347" t="s">
         <v>560</v>
       </c>
@@ -9168,7 +9348,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="348" spans="1:3">
+    <row r="348" spans="1:5">
       <c r="A348" t="s">
         <v>562</v>
       </c>
@@ -9179,7 +9359,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="349" spans="1:3">
+    <row r="349" spans="1:5">
       <c r="A349" t="s">
         <v>563</v>
       </c>
@@ -9190,7 +9370,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="350" spans="1:3">
+    <row r="350" spans="1:5">
       <c r="A350" t="s">
         <v>565</v>
       </c>
@@ -9201,7 +9381,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="351" spans="1:3">
+    <row r="351" spans="1:5">
       <c r="A351" t="s">
         <v>567</v>
       </c>
@@ -9212,7 +9392,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="352" spans="1:3">
+    <row r="352" spans="1:5">
       <c r="A352" t="s">
         <v>568</v>
       </c>
@@ -9223,7 +9403,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="353" spans="1:3">
+    <row r="353" spans="1:6">
       <c r="A353" t="s">
         <v>570</v>
       </c>
@@ -9234,7 +9414,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="354" spans="1:3">
+    <row r="354" spans="1:6">
       <c r="A354" t="s">
         <v>572</v>
       </c>
@@ -9245,7 +9425,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="355" spans="1:3">
+    <row r="355" spans="1:6">
       <c r="A355" s="10" t="s">
         <v>573</v>
       </c>
@@ -9270,7 +9450,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="357" spans="1:3">
+    <row r="357" spans="1:6">
       <c r="A357" t="s">
         <v>577</v>
       </c>
@@ -9281,7 +9461,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="358" spans="1:3">
+    <row r="358" spans="1:6">
       <c r="A358" t="s">
         <v>579</v>
       </c>
@@ -9292,7 +9472,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="359" spans="1:3">
+    <row r="359" spans="1:6">
       <c r="A359" t="s">
         <v>580</v>
       </c>
@@ -9303,7 +9483,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="360" spans="1:3">
+    <row r="360" spans="1:6">
       <c r="A360" t="s">
         <v>582</v>
       </c>
@@ -9314,7 +9494,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="361" spans="1:3">
+    <row r="361" spans="1:6">
       <c r="A361" t="s">
         <v>583</v>
       </c>
@@ -9325,7 +9505,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="362" spans="1:3">
+    <row r="362" spans="1:6">
       <c r="A362" t="s">
         <v>585</v>
       </c>
@@ -9336,7 +9516,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="363" spans="1:3">
+    <row r="363" spans="1:6">
       <c r="A363" t="s">
         <v>587</v>
       </c>
@@ -9347,7 +9527,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="364" spans="1:5">
+    <row r="364" spans="1:6">
       <c r="A364" t="s">
         <v>589</v>
       </c>
@@ -9361,7 +9541,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="365" spans="1:5">
+    <row r="365" spans="1:6">
       <c r="A365" t="s">
         <v>592</v>
       </c>
@@ -9375,7 +9555,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="366" spans="1:3">
+    <row r="366" spans="1:6">
       <c r="A366" t="s">
         <v>595</v>
       </c>
@@ -9386,7 +9566,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="367" spans="1:3">
+    <row r="367" spans="1:6">
       <c r="A367" t="s">
         <v>596</v>
       </c>
@@ -9397,7 +9577,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="368" spans="1:3">
+    <row r="368" spans="1:6">
       <c r="A368" t="s">
         <v>598</v>
       </c>
@@ -9408,7 +9588,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="369" spans="1:3">
+    <row r="369" spans="1:5">
       <c r="A369" t="s">
         <v>600</v>
       </c>
@@ -9433,7 +9613,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="371" spans="1:3">
+    <row r="371" spans="1:5">
       <c r="A371" s="10" t="s">
         <v>605</v>
       </c>
@@ -9444,7 +9624,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="372" spans="1:3">
+    <row r="372" spans="1:5">
       <c r="A372" t="s">
         <v>606</v>
       </c>
@@ -9455,7 +9635,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="373" spans="1:3">
+    <row r="373" spans="1:5">
       <c r="A373" t="s">
         <v>608</v>
       </c>
@@ -9466,7 +9646,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="374" spans="1:3">
+    <row r="374" spans="1:5">
       <c r="A374" t="s">
         <v>610</v>
       </c>
@@ -9477,7 +9657,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="375" spans="1:3">
+    <row r="375" spans="1:5">
       <c r="A375" t="s">
         <v>612</v>
       </c>
@@ -9488,7 +9668,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="376" spans="1:3">
+    <row r="376" spans="1:5">
       <c r="A376" t="s">
         <v>614</v>
       </c>
@@ -9499,7 +9679,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="377" spans="1:3">
+    <row r="377" spans="1:5">
       <c r="A377" s="10" t="s">
         <v>616</v>
       </c>
@@ -9510,7 +9690,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="378" spans="1:3">
+    <row r="378" spans="1:5">
       <c r="A378" t="s">
         <v>618</v>
       </c>
@@ -9521,7 +9701,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="379" spans="1:3">
+    <row r="379" spans="1:5">
       <c r="A379" t="s">
         <v>620</v>
       </c>
@@ -9532,7 +9712,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="380" spans="1:3">
+    <row r="380" spans="1:5">
       <c r="A380" t="s">
         <v>621</v>
       </c>
@@ -9543,7 +9723,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="381" spans="1:3">
+    <row r="381" spans="1:5">
       <c r="A381" t="s">
         <v>623</v>
       </c>
@@ -9554,7 +9734,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="382" spans="1:3">
+    <row r="382" spans="1:5">
       <c r="A382" t="s">
         <v>625</v>
       </c>
@@ -9579,7 +9759,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="384" spans="1:3">
+    <row r="384" spans="1:5">
       <c r="A384" t="s">
         <v>630</v>
       </c>
@@ -9604,7 +9784,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="386" spans="1:3">
+    <row r="386" spans="1:5">
       <c r="A386" t="s">
         <v>633</v>
       </c>
@@ -9615,7 +9795,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="387" spans="1:3">
+    <row r="387" spans="1:5">
       <c r="A387" t="s">
         <v>634</v>
       </c>
@@ -9640,7 +9820,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="389" spans="1:3">
+    <row r="389" spans="1:5">
       <c r="A389" t="s">
         <v>638</v>
       </c>
@@ -9651,7 +9831,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="390" spans="1:3">
+    <row r="390" spans="1:5">
       <c r="A390" t="s">
         <v>640</v>
       </c>
@@ -9662,7 +9842,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="391" spans="1:4">
+    <row r="391" spans="1:5">
       <c r="A391" t="s">
         <v>641</v>
       </c>
@@ -9676,7 +9856,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="392" spans="1:3">
+    <row r="392" spans="1:5">
       <c r="A392" t="s">
         <v>643</v>
       </c>
@@ -9687,7 +9867,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="393" spans="1:3">
+    <row r="393" spans="1:5">
       <c r="A393" t="s">
         <v>645</v>
       </c>
@@ -9698,7 +9878,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="394" spans="1:3">
+    <row r="394" spans="1:5">
       <c r="A394" t="s">
         <v>647</v>
       </c>
@@ -9723,7 +9903,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="396" spans="1:3">
+    <row r="396" spans="1:5">
       <c r="A396" t="s">
         <v>652</v>
       </c>
@@ -9748,7 +9928,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="398" spans="1:3">
+    <row r="398" spans="1:5">
       <c r="A398" t="s">
         <v>657</v>
       </c>
@@ -9759,7 +9939,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="399" spans="1:3">
+    <row r="399" spans="1:5">
       <c r="A399" t="s">
         <v>659</v>
       </c>
@@ -9770,7 +9950,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="400" spans="1:3">
+    <row r="400" spans="1:5">
       <c r="A400" t="s">
         <v>660</v>
       </c>
@@ -9781,7 +9961,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="401" spans="1:3">
+    <row r="401" spans="1:5">
       <c r="A401" t="s">
         <v>661</v>
       </c>
@@ -9806,7 +9986,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="403" spans="1:3">
+    <row r="403" spans="1:5">
       <c r="A403" t="s">
         <v>664</v>
       </c>
@@ -9817,7 +9997,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="404" spans="1:3">
+    <row r="404" spans="1:5">
       <c r="A404" t="s">
         <v>665</v>
       </c>
@@ -9828,7 +10008,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="405" spans="1:3">
+    <row r="405" spans="1:5">
       <c r="A405" t="s">
         <v>666</v>
       </c>
@@ -9839,7 +10019,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="406" spans="1:3">
+    <row r="406" spans="1:5">
       <c r="A406" t="s">
         <v>667</v>
       </c>
@@ -9850,7 +10030,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="407" spans="1:3">
+    <row r="407" spans="1:5">
       <c r="A407" t="s">
         <v>668</v>
       </c>
@@ -9861,7 +10041,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="408" spans="1:3">
+    <row r="408" spans="1:5">
       <c r="A408" t="s">
         <v>670</v>
       </c>
@@ -9872,7 +10052,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="409" spans="1:3">
+    <row r="409" spans="1:5">
       <c r="A409" t="s">
         <v>672</v>
       </c>
@@ -9883,7 +10063,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="410" spans="1:3">
+    <row r="410" spans="1:5">
       <c r="A410" t="s">
         <v>674</v>
       </c>
@@ -9894,7 +10074,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="411" spans="1:3">
+    <row r="411" spans="1:5">
       <c r="A411" t="s">
         <v>675</v>
       </c>
@@ -9905,7 +10085,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="412" spans="1:3">
+    <row r="412" spans="1:5">
       <c r="A412" t="s">
         <v>676</v>
       </c>
@@ -9916,7 +10096,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="413" spans="1:3">
+    <row r="413" spans="1:5">
       <c r="A413" t="s">
         <v>677</v>
       </c>
@@ -9941,7 +10121,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="415" spans="1:3">
+    <row r="415" spans="1:5">
       <c r="A415" t="s">
         <v>680</v>
       </c>
@@ -9952,7 +10132,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="416" spans="1:3">
+    <row r="416" spans="1:5">
       <c r="A416" t="s">
         <v>681</v>
       </c>
@@ -9963,7 +10143,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="417" spans="1:3">
+    <row r="417" spans="1:6">
       <c r="A417" t="s">
         <v>682</v>
       </c>
@@ -9974,7 +10154,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="418" spans="1:5">
+    <row r="418" spans="1:6">
       <c r="A418" t="s">
         <v>683</v>
       </c>
@@ -9988,7 +10168,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="419" spans="1:3">
+    <row r="419" spans="1:6">
       <c r="A419" t="s">
         <v>685</v>
       </c>
@@ -9999,7 +10179,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="420" spans="1:3">
+    <row r="420" spans="1:6">
       <c r="A420" t="s">
         <v>686</v>
       </c>
@@ -10010,7 +10190,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="421" spans="1:5">
+    <row r="421" spans="1:6">
       <c r="A421" t="s">
         <v>687</v>
       </c>
@@ -10041,7 +10221,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="423" spans="1:3">
+    <row r="423" spans="1:6">
       <c r="A423" t="s">
         <v>692</v>
       </c>
@@ -10052,7 +10232,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="424" spans="1:3">
+    <row r="424" spans="1:6">
       <c r="A424" t="s">
         <v>693</v>
       </c>
@@ -10063,7 +10243,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="425" spans="1:3">
+    <row r="425" spans="1:6">
       <c r="A425" t="s">
         <v>694</v>
       </c>
@@ -10074,7 +10254,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="426" spans="1:3">
+    <row r="426" spans="1:6">
       <c r="A426" t="s">
         <v>695</v>
       </c>
@@ -10085,7 +10265,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="427" spans="1:3">
+    <row r="427" spans="1:6">
       <c r="A427" s="10" t="s">
         <v>696</v>
       </c>
@@ -10096,7 +10276,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="428" spans="1:3">
+    <row r="428" spans="1:6">
       <c r="A428" t="s">
         <v>697</v>
       </c>
@@ -10107,7 +10287,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="429" spans="1:3">
+    <row r="429" spans="1:6">
       <c r="A429" t="s">
         <v>699</v>
       </c>
@@ -10118,7 +10298,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="430" spans="1:3">
+    <row r="430" spans="1:6">
       <c r="A430" t="s">
         <v>701</v>
       </c>
@@ -10129,7 +10309,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="431" spans="1:3">
+    <row r="431" spans="1:6">
       <c r="A431" t="s">
         <v>703</v>
       </c>
@@ -10140,7 +10320,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="432" spans="1:3">
+    <row r="432" spans="1:6">
       <c r="A432" t="s">
         <v>705</v>
       </c>
@@ -10151,7 +10331,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="433" spans="1:3">
+    <row r="433" spans="1:5">
       <c r="A433" s="8" t="s">
         <v>707</v>
       </c>
@@ -10162,7 +10342,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="434" spans="1:3">
+    <row r="434" spans="1:5">
       <c r="A434" t="s">
         <v>709</v>
       </c>
@@ -10173,7 +10353,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="435" spans="1:3">
+    <row r="435" spans="1:5">
       <c r="A435" t="s">
         <v>711</v>
       </c>
@@ -10210,7 +10390,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="438" spans="1:3">
+    <row r="438" spans="1:5">
       <c r="A438" t="s">
         <v>717</v>
       </c>
@@ -10221,7 +10401,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="439" spans="1:3">
+    <row r="439" spans="1:5">
       <c r="A439" t="s">
         <v>719</v>
       </c>
@@ -10260,7 +10440,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="442" spans="1:3">
+    <row r="442" spans="1:5">
       <c r="A442" t="s">
         <v>727</v>
       </c>
@@ -10271,7 +10451,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="443" spans="1:3">
+    <row r="443" spans="1:5">
       <c r="A443" t="s">
         <v>729</v>
       </c>
@@ -10296,7 +10476,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="445" spans="1:3">
+    <row r="445" spans="1:5">
       <c r="A445" t="s">
         <v>733</v>
       </c>
@@ -10307,7 +10487,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="446" spans="1:3">
+    <row r="446" spans="1:5">
       <c r="A446" t="s">
         <v>734</v>
       </c>
@@ -10318,7 +10498,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="447" spans="1:3">
+    <row r="447" spans="1:5">
       <c r="A447" t="s">
         <v>735</v>
       </c>
@@ -10329,7 +10509,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="448" spans="1:3">
+    <row r="448" spans="1:5">
       <c r="A448" t="s">
         <v>736</v>
       </c>
@@ -10340,7 +10520,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="449" spans="1:3">
+    <row r="449" spans="1:6">
       <c r="A449" t="s">
         <v>738</v>
       </c>
@@ -10351,7 +10531,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="450" spans="1:3">
+    <row r="450" spans="1:6">
       <c r="A450" t="s">
         <v>740</v>
       </c>
@@ -10362,7 +10542,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="451" spans="1:3">
+    <row r="451" spans="1:6">
       <c r="A451" t="s">
         <v>742</v>
       </c>
@@ -10373,7 +10553,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="452" spans="1:3">
+    <row r="452" spans="1:6">
       <c r="A452" t="s">
         <v>744</v>
       </c>
@@ -10384,7 +10564,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="453" spans="1:3">
+    <row r="453" spans="1:6">
       <c r="A453" t="s">
         <v>746</v>
       </c>
@@ -10395,7 +10575,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="454" spans="1:5">
+    <row r="454" spans="1:6">
       <c r="A454" t="s">
         <v>748</v>
       </c>
@@ -10409,7 +10589,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="455" spans="1:3">
+    <row r="455" spans="1:6">
       <c r="A455" t="s">
         <v>750</v>
       </c>
@@ -10420,7 +10600,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="456" spans="1:5">
+    <row r="456" spans="1:6">
       <c r="A456" t="s">
         <v>751</v>
       </c>
@@ -10434,7 +10614,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="457" spans="1:4">
+    <row r="457" spans="1:6">
       <c r="A457" s="10" t="s">
         <v>753</v>
       </c>
@@ -10446,7 +10626,7 @@
       </c>
       <c r="D457" s="11"/>
     </row>
-    <row r="458" spans="1:3">
+    <row r="458" spans="1:6">
       <c r="A458" s="10" t="s">
         <v>754</v>
       </c>
@@ -10457,7 +10637,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="459" spans="1:3">
+    <row r="459" spans="1:6">
       <c r="A459" t="s">
         <v>755</v>
       </c>
@@ -10468,7 +10648,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="460" spans="1:3">
+    <row r="460" spans="1:6">
       <c r="A460" t="s">
         <v>757</v>
       </c>
@@ -10479,7 +10659,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="461" spans="1:3">
+    <row r="461" spans="1:6">
       <c r="A461" t="s">
         <v>759</v>
       </c>
@@ -10490,7 +10670,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="462" spans="1:5">
+    <row r="462" spans="1:6">
       <c r="A462" t="s">
         <v>760</v>
       </c>
@@ -10518,7 +10698,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="464" spans="1:3">
+    <row r="464" spans="1:6">
       <c r="A464" s="10" t="s">
         <v>764</v>
       </c>
@@ -10705,7 +10885,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="481" spans="1:3">
+    <row r="481" spans="1:6">
       <c r="A481" t="s">
         <v>791</v>
       </c>
@@ -10716,7 +10896,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="482" spans="1:3">
+    <row r="482" spans="1:6">
       <c r="A482" t="s">
         <v>793</v>
       </c>
@@ -10727,7 +10907,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="483" spans="1:3">
+    <row r="483" spans="1:6">
       <c r="A483" t="s">
         <v>795</v>
       </c>
@@ -10738,7 +10918,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="484" spans="1:3">
+    <row r="484" spans="1:6">
       <c r="A484" t="s">
         <v>797</v>
       </c>
@@ -10749,7 +10929,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="485" spans="1:3">
+    <row r="485" spans="1:6">
       <c r="A485" t="s">
         <v>799</v>
       </c>
@@ -10760,7 +10940,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="486" ht="14.25" spans="1:3">
+    <row r="486" ht="14.25" spans="1:6">
       <c r="A486" t="s">
         <v>522</v>
       </c>
@@ -10771,7 +10951,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="487" spans="1:3">
+    <row r="487" spans="1:6">
       <c r="A487" t="s">
         <v>802</v>
       </c>
@@ -10782,7 +10962,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="488" spans="1:3">
+    <row r="488" spans="1:6">
       <c r="A488" t="s">
         <v>804</v>
       </c>
@@ -10793,7 +10973,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="489" spans="1:3">
+    <row r="489" spans="1:6">
       <c r="A489" t="s">
         <v>806</v>
       </c>
@@ -10832,7 +11012,7 @@
         <v>2534165585</v>
       </c>
     </row>
-    <row r="492" spans="1:3">
+    <row r="492" spans="1:6">
       <c r="A492" t="s">
         <v>810</v>
       </c>
@@ -10843,7 +11023,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="493" spans="1:3">
+    <row r="493" spans="1:6">
       <c r="A493" t="s">
         <v>812</v>
       </c>
@@ -10854,7 +11034,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="494" spans="1:3">
+    <row r="494" spans="1:6">
       <c r="A494" t="s">
         <v>813</v>
       </c>
@@ -10865,7 +11045,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="495" spans="1:5">
+    <row r="495" spans="1:6">
       <c r="A495" t="s">
         <v>815</v>
       </c>
@@ -10879,7 +11059,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="496" spans="1:5">
+    <row r="496" spans="1:6">
       <c r="A496" t="s">
         <v>818</v>
       </c>
@@ -10893,7 +11073,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="497" spans="1:3">
+    <row r="497" spans="1:5">
       <c r="A497" t="s">
         <v>821</v>
       </c>
@@ -10904,7 +11084,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="498" spans="1:3">
+    <row r="498" spans="1:5">
       <c r="A498" t="s">
         <v>823</v>
       </c>
@@ -10915,7 +11095,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="499" spans="1:3">
+    <row r="499" spans="1:5">
       <c r="A499" t="s">
         <v>824</v>
       </c>
@@ -10926,7 +11106,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="500" spans="1:3">
+    <row r="500" spans="1:5">
       <c r="A500" t="s">
         <v>826</v>
       </c>
@@ -10937,7 +11117,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="501" spans="1:3">
+    <row r="501" spans="1:5">
       <c r="A501" t="s">
         <v>828</v>
       </c>
@@ -10948,7 +11128,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="502" spans="1:3">
+    <row r="502" spans="1:5">
       <c r="A502" t="s">
         <v>829</v>
       </c>
@@ -10959,7 +11139,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="503" spans="1:3">
+    <row r="503" spans="1:5">
       <c r="A503" t="s">
         <v>830</v>
       </c>
@@ -10984,7 +11164,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="505" spans="1:3">
+    <row r="505" spans="1:5">
       <c r="A505" t="s">
         <v>833</v>
       </c>
@@ -10995,7 +11175,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="506" spans="1:3">
+    <row r="506" spans="1:5">
       <c r="A506" t="s">
         <v>835</v>
       </c>
@@ -11006,7 +11186,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="507" spans="1:3">
+    <row r="507" spans="1:5">
       <c r="A507" t="s">
         <v>837</v>
       </c>
@@ -11031,7 +11211,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="509" spans="1:3">
+    <row r="509" spans="1:5">
       <c r="A509" t="s">
         <v>840</v>
       </c>
@@ -11042,7 +11222,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="510" spans="1:3">
+    <row r="510" spans="1:5">
       <c r="A510" t="s">
         <v>841</v>
       </c>
@@ -11053,7 +11233,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="511" spans="1:3">
+    <row r="511" spans="1:5">
       <c r="A511" t="s">
         <v>842</v>
       </c>
@@ -11064,7 +11244,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="512" spans="1:3">
+    <row r="512" spans="1:5">
       <c r="A512" t="s">
         <v>843</v>
       </c>
@@ -11075,7 +11255,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="513" spans="1:5">
+    <row r="513" spans="1:6">
       <c r="A513" t="s">
         <v>844</v>
       </c>
@@ -11089,7 +11269,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="514" spans="1:3">
+    <row r="514" spans="1:6">
       <c r="A514" t="s">
         <v>846</v>
       </c>
@@ -11100,7 +11280,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="515" spans="1:3">
+    <row r="515" spans="1:6">
       <c r="A515" t="s">
         <v>848</v>
       </c>
@@ -11111,7 +11291,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="516" spans="1:3">
+    <row r="516" spans="1:6">
       <c r="A516" t="s">
         <v>850</v>
       </c>
@@ -11122,7 +11302,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="517" spans="1:3">
+    <row r="517" spans="1:6">
       <c r="A517" t="s">
         <v>851</v>
       </c>
@@ -11147,7 +11327,7 @@
         <v>2536595683</v>
       </c>
     </row>
-    <row r="519" spans="1:3">
+    <row r="519" spans="1:6">
       <c r="A519" t="s">
         <v>853</v>
       </c>
@@ -11158,7 +11338,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="520" spans="1:3">
+    <row r="520" spans="1:6">
       <c r="A520" t="s">
         <v>855</v>
       </c>
@@ -11169,7 +11349,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="521" spans="1:3">
+    <row r="521" spans="1:6">
       <c r="A521" t="s">
         <v>857</v>
       </c>
@@ -11180,7 +11360,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="522" spans="1:3">
+    <row r="522" spans="1:6">
       <c r="A522" t="s">
         <v>858</v>
       </c>
@@ -11191,7 +11371,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="523" spans="1:3">
+    <row r="523" spans="1:6">
       <c r="A523" t="s">
         <v>859</v>
       </c>
@@ -11202,7 +11382,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="524" spans="1:3">
+    <row r="524" spans="1:6">
       <c r="A524" t="s">
         <v>860</v>
       </c>
@@ -11213,7 +11393,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="525" spans="1:3">
+    <row r="525" spans="1:6">
       <c r="A525" t="s">
         <v>861</v>
       </c>
@@ -11224,7 +11404,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="526" spans="1:3">
+    <row r="526" spans="1:6">
       <c r="A526" t="s">
         <v>862</v>
       </c>
@@ -11235,7 +11415,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="527" spans="1:3">
+    <row r="527" spans="1:6">
       <c r="A527" t="s">
         <v>863</v>
       </c>
@@ -11246,7 +11426,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="528" spans="1:3">
+    <row r="528" spans="1:6">
       <c r="A528" t="s">
         <v>864</v>
       </c>
@@ -11257,7 +11437,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="529" spans="1:5">
+    <row r="529" spans="1:6">
       <c r="A529" s="8" t="s">
         <v>866</v>
       </c>
@@ -11269,7 +11449,7 @@
       </c>
       <c r="E529" s="9"/>
     </row>
-    <row r="530" spans="1:3">
+    <row r="530" spans="1:6">
       <c r="A530" t="s">
         <v>867</v>
       </c>
@@ -11280,7 +11460,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="531" spans="1:3">
+    <row r="531" spans="1:6">
       <c r="A531" t="s">
         <v>868</v>
       </c>
@@ -11291,7 +11471,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="532" spans="1:3">
+    <row r="532" spans="1:6">
       <c r="A532" t="s">
         <v>869</v>
       </c>
@@ -11302,7 +11482,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="533" spans="1:3">
+    <row r="533" spans="1:6">
       <c r="A533" t="s">
         <v>870</v>
       </c>
@@ -11313,7 +11493,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="534" spans="1:5">
+    <row r="534" spans="1:6">
       <c r="A534" t="s">
         <v>871</v>
       </c>
@@ -11327,7 +11507,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="535" spans="1:3">
+    <row r="535" spans="1:6">
       <c r="A535" t="s">
         <v>874</v>
       </c>
@@ -11352,7 +11532,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="537" spans="1:3">
+    <row r="537" spans="1:6">
       <c r="A537" t="s">
         <v>878</v>
       </c>
@@ -11363,7 +11543,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="538" spans="1:3">
+    <row r="538" spans="1:6">
       <c r="A538" t="s">
         <v>880</v>
       </c>
@@ -11374,7 +11554,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="539" spans="1:3">
+    <row r="539" spans="1:6">
       <c r="A539" t="s">
         <v>882</v>
       </c>
@@ -11385,7 +11565,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="540" spans="1:3">
+    <row r="540" spans="1:6">
       <c r="A540" t="s">
         <v>884</v>
       </c>
@@ -11396,7 +11576,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="541" spans="1:5">
+    <row r="541" spans="1:6">
       <c r="A541" s="8" t="s">
         <v>885</v>
       </c>
@@ -11408,7 +11588,7 @@
       </c>
       <c r="E541" s="9"/>
     </row>
-    <row r="542" spans="1:3">
+    <row r="542" spans="1:6">
       <c r="A542" t="s">
         <v>886</v>
       </c>
@@ -11419,7 +11599,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="543" spans="1:3">
+    <row r="543" spans="1:6">
       <c r="A543" t="s">
         <v>887</v>
       </c>
@@ -11430,7 +11610,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="544" spans="1:3">
+    <row r="544" spans="1:6">
       <c r="A544" t="s">
         <v>888</v>
       </c>
@@ -11441,7 +11621,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="545" spans="1:3">
+    <row r="545" spans="1:5">
       <c r="A545" t="s">
         <v>889</v>
       </c>
@@ -11466,7 +11646,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="547" spans="1:3">
+    <row r="547" spans="1:5">
       <c r="A547" t="s">
         <v>892</v>
       </c>
@@ -11477,7 +11657,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="548" spans="1:3">
+    <row r="548" spans="1:5">
       <c r="A548" t="s">
         <v>893</v>
       </c>
@@ -11488,7 +11668,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="549" spans="1:3">
+    <row r="549" spans="1:5">
       <c r="A549" s="10" t="s">
         <v>894</v>
       </c>
@@ -11499,7 +11679,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="550" spans="1:3">
+    <row r="550" spans="1:5">
       <c r="A550" t="s">
         <v>895</v>
       </c>
@@ -11510,7 +11690,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="551" spans="1:3">
+    <row r="551" spans="1:5">
       <c r="A551" t="s">
         <v>897</v>
       </c>
@@ -11535,7 +11715,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="553" spans="1:3">
+    <row r="553" spans="1:5">
       <c r="A553" t="s">
         <v>901</v>
       </c>
@@ -11546,7 +11726,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="554" spans="1:3">
+    <row r="554" spans="1:5">
       <c r="A554" s="8" t="s">
         <v>902</v>
       </c>
@@ -11557,7 +11737,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="555" spans="1:3">
+    <row r="555" spans="1:5">
       <c r="A555" t="s">
         <v>903</v>
       </c>
@@ -11568,7 +11748,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="556" spans="1:3">
+    <row r="556" spans="1:5">
       <c r="A556" t="s">
         <v>904</v>
       </c>
@@ -11579,7 +11759,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="557" spans="1:3">
+    <row r="557" spans="1:5">
       <c r="A557" t="s">
         <v>906</v>
       </c>
@@ -11604,7 +11784,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="559" spans="1:3">
+    <row r="559" spans="1:5">
       <c r="A559" s="8" t="s">
         <v>907</v>
       </c>
@@ -11629,7 +11809,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="561" spans="1:3">
+    <row r="561" spans="1:5">
       <c r="A561" t="s">
         <v>913</v>
       </c>
@@ -11640,7 +11820,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="562" spans="1:3">
+    <row r="562" spans="1:5">
       <c r="A562" t="s">
         <v>915</v>
       </c>
@@ -11651,7 +11831,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="563" spans="1:3">
+    <row r="563" spans="1:5">
       <c r="A563" t="s">
         <v>916</v>
       </c>
@@ -11662,7 +11842,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="564" spans="1:3">
+    <row r="564" spans="1:5">
       <c r="A564" t="s">
         <v>918</v>
       </c>
@@ -11673,7 +11853,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="565" spans="1:3">
+    <row r="565" spans="1:5">
       <c r="A565" t="s">
         <v>919</v>
       </c>
@@ -11684,7 +11864,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="566" spans="1:3">
+    <row r="566" spans="1:5">
       <c r="A566" t="s">
         <v>920</v>
       </c>
@@ -11695,7 +11875,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="567" spans="1:3">
+    <row r="567" spans="1:5">
       <c r="A567" s="10" t="s">
         <v>921</v>
       </c>
@@ -11706,7 +11886,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="568" spans="1:3">
+    <row r="568" spans="1:5">
       <c r="A568" t="s">
         <v>922</v>
       </c>
@@ -11717,7 +11897,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="569" spans="1:3">
+    <row r="569" spans="1:5">
       <c r="A569" t="s">
         <v>924</v>
       </c>
@@ -11728,7 +11908,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="570" spans="1:3">
+    <row r="570" spans="1:5">
       <c r="A570" t="s">
         <v>926</v>
       </c>
@@ -11739,7 +11919,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="571" spans="1:4">
+    <row r="571" spans="1:5">
       <c r="A571" s="10" t="s">
         <v>928</v>
       </c>
@@ -11751,7 +11931,7 @@
       </c>
       <c r="D571" s="11"/>
     </row>
-    <row r="572" spans="1:3">
+    <row r="572" spans="1:5">
       <c r="A572" t="s">
         <v>930</v>
       </c>
@@ -11762,7 +11942,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="573" ht="14.25" spans="1:3">
+    <row r="573" ht="14.25" spans="1:5">
       <c r="A573" s="12" t="s">
         <v>932</v>
       </c>
@@ -11773,7 +11953,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="574" spans="1:3">
+    <row r="574" spans="1:5">
       <c r="A574" t="s">
         <v>934</v>
       </c>
@@ -11794,12 +11974,11 @@
       <c r="C575" t="s">
         <v>258</v>
       </c>
-      <c r="D575" s="2"/>
       <c r="E575" t="s">
         <v>938</v>
       </c>
     </row>
-    <row r="576" spans="1:3">
+    <row r="576" spans="1:5">
       <c r="A576" t="s">
         <v>210</v>
       </c>
@@ -11810,7 +11989,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="577" spans="1:3">
+    <row r="577" spans="1:5">
       <c r="A577" t="s">
         <v>939</v>
       </c>
@@ -11821,7 +12000,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="578" spans="1:3">
+    <row r="578" spans="1:5">
       <c r="A578" t="s">
         <v>940</v>
       </c>
@@ -11832,7 +12011,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="579" spans="1:3">
+    <row r="579" spans="1:5">
       <c r="A579" s="10" t="s">
         <v>942</v>
       </c>
@@ -11843,7 +12022,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="580" spans="1:3">
+    <row r="580" spans="1:5">
       <c r="A580" t="s">
         <v>944</v>
       </c>
@@ -11854,7 +12033,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="581" spans="1:4">
+    <row r="581" spans="1:5">
       <c r="A581" s="10" t="s">
         <v>946</v>
       </c>
@@ -11876,12 +12055,11 @@
       <c r="C582" t="s">
         <v>258</v>
       </c>
-      <c r="D582" s="2"/>
       <c r="E582" t="s">
         <v>950</v>
       </c>
     </row>
-    <row r="583" spans="1:3">
+    <row r="583" spans="1:5">
       <c r="A583" t="s">
         <v>951</v>
       </c>
@@ -11892,7 +12070,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="584" spans="1:3">
+    <row r="584" spans="1:5">
       <c r="A584" t="s">
         <v>953</v>
       </c>
@@ -11903,7 +12081,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="585" spans="1:3">
+    <row r="585" spans="1:5">
       <c r="A585" t="s">
         <v>955</v>
       </c>
@@ -11914,7 +12092,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="586" spans="1:3">
+    <row r="586" spans="1:5">
       <c r="A586" t="s">
         <v>956</v>
       </c>
@@ -11925,7 +12103,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="587" spans="1:3">
+    <row r="587" spans="1:5">
       <c r="A587" t="s">
         <v>957</v>
       </c>
@@ -11936,7 +12114,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="588" spans="1:3">
+    <row r="588" spans="1:5">
       <c r="A588" t="s">
         <v>959</v>
       </c>
@@ -11947,7 +12125,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="589" spans="1:3">
+    <row r="589" spans="1:5">
       <c r="A589" t="s">
         <v>961</v>
       </c>
@@ -11958,7 +12136,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="590" spans="1:3">
+    <row r="590" spans="1:5">
       <c r="A590" t="s">
         <v>963</v>
       </c>
@@ -11969,7 +12147,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="591" spans="1:4">
+    <row r="591" spans="1:5">
       <c r="A591" t="s">
         <v>964</v>
       </c>
@@ -11983,7 +12161,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="592" spans="1:4">
+    <row r="592" spans="1:5">
       <c r="A592" t="s">
         <v>966</v>
       </c>
@@ -11997,7 +12175,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="593" spans="1:3">
+    <row r="593" spans="1:5">
       <c r="A593" s="10" t="s">
         <v>967</v>
       </c>
@@ -12020,7 +12198,7 @@
       </c>
       <c r="E594" s="9"/>
     </row>
-    <row r="595" spans="1:3">
+    <row r="595" spans="1:5">
       <c r="A595" s="10" t="s">
         <v>971</v>
       </c>
@@ -12045,7 +12223,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="597" spans="1:3">
+    <row r="597" spans="1:5">
       <c r="A597" t="s">
         <v>976</v>
       </c>
@@ -12070,7 +12248,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="599" spans="1:3">
+    <row r="599" spans="1:5">
       <c r="A599" t="s">
         <v>980</v>
       </c>
@@ -12081,7 +12259,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="600" spans="1:3">
+    <row r="600" spans="1:5">
       <c r="A600" t="s">
         <v>982</v>
       </c>
@@ -12106,7 +12284,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="602" spans="1:4">
+    <row r="602" spans="1:5">
       <c r="A602" s="10" t="s">
         <v>987</v>
       </c>
@@ -12144,7 +12322,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="605" spans="1:3">
+    <row r="605" spans="1:5">
       <c r="A605" t="s">
         <v>994</v>
       </c>
@@ -12155,7 +12333,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="606" spans="1:3">
+    <row r="606" spans="1:5">
       <c r="A606" t="s">
         <v>995</v>
       </c>
@@ -12166,7 +12344,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="607" spans="1:3">
+    <row r="607" spans="1:5">
       <c r="A607" t="s">
         <v>996</v>
       </c>
@@ -12177,7 +12355,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="608" spans="1:3">
+    <row r="608" spans="1:5">
       <c r="A608" t="s">
         <v>998</v>
       </c>
@@ -12188,7 +12366,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="609" spans="1:3">
+    <row r="609" spans="1:5">
       <c r="A609" t="s">
         <v>999</v>
       </c>
@@ -12199,7 +12377,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="610" spans="1:3">
+    <row r="610" spans="1:5">
       <c r="A610" t="s">
         <v>1000</v>
       </c>
@@ -12210,7 +12388,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="611" spans="1:3">
+    <row r="611" spans="1:5">
       <c r="A611" t="s">
         <v>1002</v>
       </c>
@@ -12221,7 +12399,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="612" spans="1:3">
+    <row r="612" spans="1:5">
       <c r="A612" t="s">
         <v>1004</v>
       </c>
@@ -12232,7 +12410,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="613" spans="1:3">
+    <row r="613" spans="1:5">
       <c r="A613" t="s">
         <v>1005</v>
       </c>
@@ -12243,7 +12421,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="614" spans="1:3">
+    <row r="614" spans="1:5">
       <c r="A614" t="s">
         <v>1006</v>
       </c>
@@ -12254,7 +12432,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="615" spans="1:3">
+    <row r="615" spans="1:5">
       <c r="A615" t="s">
         <v>1007</v>
       </c>
@@ -12265,7 +12443,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="616" spans="1:3">
+    <row r="616" spans="1:5">
       <c r="A616" t="s">
         <v>1008</v>
       </c>
@@ -12276,7 +12454,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="617" spans="1:3">
+    <row r="617" spans="1:5">
       <c r="A617" t="s">
         <v>1010</v>
       </c>
@@ -12287,7 +12465,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="618" spans="1:3">
+    <row r="618" spans="1:5">
       <c r="A618" t="s">
         <v>1012</v>
       </c>
@@ -12298,7 +12476,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="619" spans="1:3">
+    <row r="619" spans="1:5">
       <c r="A619" t="s">
         <v>1014</v>
       </c>
@@ -12309,7 +12487,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="620" spans="1:3">
+    <row r="620" spans="1:5">
       <c r="A620" t="s">
         <v>1016</v>
       </c>
@@ -12334,7 +12512,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="622" spans="1:3">
+    <row r="622" spans="1:5">
       <c r="A622" t="s">
         <v>308</v>
       </c>
@@ -12345,7 +12523,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="623" spans="1:3">
+    <row r="623" spans="1:5">
       <c r="A623" t="s">
         <v>1022</v>
       </c>
@@ -12356,7 +12534,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="624" spans="1:3">
+    <row r="624" spans="1:5">
       <c r="A624" s="10" t="s">
         <v>1024</v>
       </c>
@@ -12367,7 +12545,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="625" spans="1:5">
+    <row r="625" spans="1:6">
       <c r="A625" t="s">
         <v>1025</v>
       </c>
@@ -12381,7 +12559,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="626" spans="1:3">
+    <row r="626" spans="1:6">
       <c r="A626" t="s">
         <v>1028</v>
       </c>
@@ -12392,7 +12570,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="627" spans="1:3">
+    <row r="627" spans="1:6">
       <c r="A627" t="s">
         <v>1030</v>
       </c>
@@ -12403,7 +12581,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="628" spans="1:3">
+    <row r="628" spans="1:6">
       <c r="A628" t="s">
         <v>1032</v>
       </c>
@@ -12414,7 +12592,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="629" spans="1:3">
+    <row r="629" spans="1:6">
       <c r="A629" t="s">
         <v>1034</v>
       </c>
@@ -12425,7 +12603,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="630" spans="1:5">
+    <row r="630" spans="1:6">
       <c r="A630" t="s">
         <v>1035</v>
       </c>
@@ -12439,7 +12617,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="631" spans="1:3">
+    <row r="631" spans="1:6">
       <c r="A631" t="s">
         <v>1038</v>
       </c>
@@ -12450,7 +12628,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="632" spans="1:3">
+    <row r="632" spans="1:6">
       <c r="A632" t="s">
         <v>1039</v>
       </c>
@@ -12461,7 +12639,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="633" spans="1:3">
+    <row r="633" spans="1:6">
       <c r="A633" t="s">
         <v>1041</v>
       </c>
@@ -12472,7 +12650,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="634" spans="1:3">
+    <row r="634" spans="1:6">
       <c r="A634" t="s">
         <v>1043</v>
       </c>
@@ -12483,7 +12661,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="635" spans="1:5">
+    <row r="635" spans="1:6">
       <c r="A635" t="s">
         <v>1044</v>
       </c>
@@ -12511,7 +12689,7 @@
         <v>2533635607</v>
       </c>
     </row>
-    <row r="637" spans="1:3">
+    <row r="637" spans="1:6">
       <c r="A637" t="s">
         <v>1047</v>
       </c>
@@ -12522,7 +12700,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="638" spans="1:3">
+    <row r="638" spans="1:6">
       <c r="A638" t="s">
         <v>1048</v>
       </c>
@@ -12533,7 +12711,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="639" spans="1:3">
+    <row r="639" spans="1:6">
       <c r="A639" t="s">
         <v>1050</v>
       </c>
@@ -12544,7 +12722,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="640" spans="1:3">
+    <row r="640" spans="1:6">
       <c r="A640" t="s">
         <v>1051</v>
       </c>
@@ -12555,7 +12733,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="641" spans="1:3">
+    <row r="641" spans="1:5">
       <c r="A641" t="s">
         <v>1052</v>
       </c>
@@ -12566,7 +12744,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="642" spans="1:3">
+    <row r="642" spans="1:5">
       <c r="A642" t="s">
         <v>1053</v>
       </c>
@@ -12577,7 +12755,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="643" spans="1:3">
+    <row r="643" spans="1:5">
       <c r="A643" t="s">
         <v>1054</v>
       </c>
@@ -12588,7 +12766,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="644" spans="1:3">
+    <row r="644" spans="1:5">
       <c r="A644" t="s">
         <v>1055</v>
       </c>
@@ -12599,7 +12777,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="645" spans="1:3">
+    <row r="645" spans="1:5">
       <c r="A645" t="s">
         <v>1056</v>
       </c>
@@ -12610,7 +12788,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="646" spans="1:3">
+    <row r="646" spans="1:5">
       <c r="A646" t="s">
         <v>1057</v>
       </c>
@@ -12621,7 +12799,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="647" spans="1:3">
+    <row r="647" spans="1:5">
       <c r="A647" t="s">
         <v>1058</v>
       </c>
@@ -12632,7 +12810,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="648" spans="1:3">
+    <row r="648" spans="1:5">
       <c r="A648" t="s">
         <v>1060</v>
       </c>
@@ -12657,7 +12835,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="650" spans="1:3">
+    <row r="650" spans="1:5">
       <c r="A650" t="s">
         <v>1065</v>
       </c>
@@ -12668,7 +12846,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="651" spans="1:3">
+    <row r="651" spans="1:5">
       <c r="A651" t="s">
         <v>1067</v>
       </c>
@@ -12679,7 +12857,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="652" spans="1:3">
+    <row r="652" spans="1:5">
       <c r="A652" t="s">
         <v>1069</v>
       </c>
@@ -12690,7 +12868,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="653" spans="1:3">
+    <row r="653" spans="1:5">
       <c r="A653" t="s">
         <v>1071</v>
       </c>
@@ -12701,7 +12879,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="654" spans="1:3">
+    <row r="654" spans="1:5">
       <c r="A654" t="s">
         <v>1073</v>
       </c>
@@ -12712,7 +12890,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="655" spans="1:3">
+    <row r="655" spans="1:5">
       <c r="A655" t="s">
         <v>1075</v>
       </c>
@@ -12723,7 +12901,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="656" spans="1:4">
+    <row r="656" spans="1:5">
       <c r="A656" s="10" t="s">
         <v>1077</v>
       </c>
@@ -12735,7 +12913,7 @@
       </c>
       <c r="D656" s="11"/>
     </row>
-    <row r="657" spans="1:3">
+    <row r="657" spans="1:6">
       <c r="A657" t="s">
         <v>1079</v>
       </c>
@@ -12746,7 +12924,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="658" spans="1:3">
+    <row r="658" spans="1:6">
       <c r="A658" t="s">
         <v>1081</v>
       </c>
@@ -12767,12 +12945,11 @@
       <c r="C659" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="D659" s="2"/>
       <c r="F659" s="9" t="s">
         <v>1084</v>
       </c>
     </row>
-    <row r="660" spans="1:3">
+    <row r="660" spans="1:6">
       <c r="A660" t="s">
         <v>1085</v>
       </c>
@@ -12783,7 +12960,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="661" spans="1:3">
+    <row r="661" spans="1:6">
       <c r="A661" t="s">
         <v>1086</v>
       </c>
@@ -12794,7 +12971,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="662" spans="1:3">
+    <row r="662" spans="1:6">
       <c r="A662" t="s">
         <v>1087</v>
       </c>
@@ -12805,7 +12982,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="663" spans="1:3">
+    <row r="663" spans="1:6">
       <c r="A663" t="s">
         <v>1088</v>
       </c>
@@ -12816,7 +12993,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="664" spans="1:3">
+    <row r="664" spans="1:6">
       <c r="A664" t="s">
         <v>1089</v>
       </c>
@@ -12827,7 +13004,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="665" spans="1:3">
+    <row r="665" spans="1:6">
       <c r="A665" t="s">
         <v>1090</v>
       </c>
@@ -12838,7 +13015,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="666" spans="1:3">
+    <row r="666" spans="1:6">
       <c r="A666" t="s">
         <v>1091</v>
       </c>
@@ -12849,7 +13026,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="667" spans="1:3">
+    <row r="667" spans="1:6">
       <c r="A667" t="s">
         <v>1092</v>
       </c>
@@ -12860,7 +13037,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="668" spans="1:5">
+    <row r="668" spans="1:6">
       <c r="A668" t="s">
         <v>1093</v>
       </c>
@@ -12874,7 +13051,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="669" spans="1:3">
+    <row r="669" spans="1:6">
       <c r="A669" t="s">
         <v>1095</v>
       </c>
@@ -12885,7 +13062,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="670" spans="1:3">
+    <row r="670" spans="1:6">
       <c r="A670" t="s">
         <v>1096</v>
       </c>
@@ -12896,7 +13073,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="671" spans="1:3">
+    <row r="671" spans="1:6">
       <c r="A671" t="s">
         <v>1097</v>
       </c>
@@ -12907,7 +13084,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="672" spans="1:3">
+    <row r="672" spans="1:6">
       <c r="A672" t="s">
         <v>1098</v>
       </c>
@@ -12918,7 +13095,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="673" spans="1:3">
+    <row r="673" spans="1:4">
       <c r="A673" t="s">
         <v>1099</v>
       </c>
@@ -12929,7 +13106,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="674" spans="1:3">
+    <row r="674" spans="1:4">
       <c r="A674" t="s">
         <v>1100</v>
       </c>
@@ -12940,7 +13117,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="675" spans="1:3">
+    <row r="675" spans="1:4">
       <c r="A675" t="s">
         <v>1101</v>
       </c>
@@ -12951,7 +13128,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="676" spans="1:3">
+    <row r="676" spans="1:4">
       <c r="A676" t="s">
         <v>1103</v>
       </c>
@@ -12962,7 +13139,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="677" spans="1:3">
+    <row r="677" spans="1:4">
       <c r="A677" t="s">
         <v>1105</v>
       </c>
@@ -12973,7 +13150,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="678" spans="1:3">
+    <row r="678" spans="1:4">
       <c r="A678" t="s">
         <v>1107</v>
       </c>
@@ -12984,7 +13161,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="679" spans="1:3">
+    <row r="679" spans="1:4">
       <c r="A679" t="s">
         <v>1109</v>
       </c>
@@ -12995,7 +13172,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="680" spans="1:3">
+    <row r="680" spans="1:4">
       <c r="A680" t="s">
         <v>1110</v>
       </c>
@@ -13007,246 +13184,686 @@
       </c>
     </row>
     <row r="681" spans="1:4">
-      <c r="A681" s="10"/>
-      <c r="B681" s="10"/>
-      <c r="C681" s="10"/>
-      <c r="D681" s="11"/>
+      <c r="A681" s="10" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B681" s="10" t="s">
+        <v>514</v>
+      </c>
+      <c r="C681" t="s">
+        <v>258</v>
+      </c>
+      <c r="D681" s="2" t="s">
+        <v>1113</v>
+      </c>
     </row>
     <row r="682" spans="1:4">
-      <c r="A682" s="10"/>
-      <c r="B682" s="10"/>
-      <c r="C682" s="10"/>
-      <c r="D682" s="11"/>
-    </row>
-    <row r="683" spans="1:3">
-      <c r="A683" s="10"/>
-      <c r="C683" s="10"/>
+      <c r="A682" s="10" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B682" s="10" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C682" t="s">
+        <v>258</v>
+      </c>
+      <c r="D682" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="683" spans="1:4">
+      <c r="A683" s="10" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B683" t="s">
+        <v>263</v>
+      </c>
+      <c r="C683" t="s">
+        <v>258</v>
+      </c>
+      <c r="D683" s="2" t="s">
+        <v>1113</v>
+      </c>
     </row>
     <row r="684" spans="1:4">
-      <c r="A684" s="10"/>
-      <c r="B684" s="10"/>
-      <c r="C684" s="10"/>
-      <c r="D684" s="11"/>
+      <c r="A684" s="10" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B684" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C684" t="s">
+        <v>258</v>
+      </c>
+      <c r="D684" s="2" t="s">
+        <v>1113</v>
+      </c>
     </row>
     <row r="685" spans="1:4">
-      <c r="A685" s="10"/>
-      <c r="B685" s="10"/>
-      <c r="C685" s="10"/>
-      <c r="D685" s="11"/>
-    </row>
-    <row r="686" spans="1:3">
-      <c r="A686" s="10"/>
-      <c r="C686" s="10"/>
+      <c r="A685" s="10" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B685" s="10" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C685" t="s">
+        <v>258</v>
+      </c>
+      <c r="D685" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="686" spans="1:4">
+      <c r="A686" s="10" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B686" t="s">
+        <v>263</v>
+      </c>
+      <c r="C686" t="s">
+        <v>258</v>
+      </c>
+      <c r="D686" s="2" t="s">
+        <v>1113</v>
+      </c>
     </row>
     <row r="687" spans="1:4">
-      <c r="A687" s="10"/>
-      <c r="C687" s="10"/>
-      <c r="D687" s="11"/>
+      <c r="A687" s="10" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B687" t="s">
+        <v>324</v>
+      </c>
+      <c r="C687" t="s">
+        <v>258</v>
+      </c>
+      <c r="D687" s="2" t="s">
+        <v>1113</v>
+      </c>
     </row>
     <row r="688" spans="1:4">
-      <c r="A688" s="10"/>
-      <c r="C688" s="10"/>
-      <c r="D688" s="11"/>
-    </row>
-    <row r="689" spans="1:3">
-      <c r="A689" s="10"/>
-      <c r="C689" s="10"/>
-    </row>
-    <row r="690" spans="3:4">
-      <c r="C690" s="10"/>
-      <c r="D690" s="11"/>
-    </row>
-    <row r="691" spans="1:3">
-      <c r="A691" s="10"/>
-      <c r="B691" s="10"/>
-      <c r="C691" s="10"/>
-    </row>
-    <row r="692" spans="1:3">
-      <c r="A692" s="10"/>
-      <c r="B692" s="10"/>
-      <c r="C692" s="10"/>
-    </row>
-    <row r="693" spans="1:3">
-      <c r="A693" s="10"/>
-      <c r="B693" s="10"/>
-      <c r="C693" s="10"/>
+      <c r="A688" s="10" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B688" t="s">
+        <v>263</v>
+      </c>
+      <c r="C688" t="s">
+        <v>258</v>
+      </c>
+      <c r="D688" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="689" spans="1:4">
+      <c r="A689" s="10" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B689" t="s">
+        <v>263</v>
+      </c>
+      <c r="C689" t="s">
+        <v>258</v>
+      </c>
+      <c r="D689" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="690" spans="1:4">
+      <c r="A690" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B690" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C690" t="s">
+        <v>258</v>
+      </c>
+      <c r="D690" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="691" spans="1:4">
+      <c r="A691" s="10" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B691" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C691" t="s">
+        <v>258</v>
+      </c>
+      <c r="D691" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="692" spans="1:4">
+      <c r="A692" s="10" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B692" s="10" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C692" t="s">
+        <v>258</v>
+      </c>
+      <c r="D692" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="693" spans="1:4">
+      <c r="A693" s="10" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B693" s="10" t="s">
+        <v>865</v>
+      </c>
+      <c r="C693" t="s">
+        <v>258</v>
+      </c>
+      <c r="D693" s="2" t="s">
+        <v>1113</v>
+      </c>
     </row>
     <row r="694" spans="1:4">
-      <c r="A694" s="10"/>
-      <c r="C694" s="10"/>
-      <c r="D694" s="11"/>
-    </row>
-    <row r="695" spans="1:3">
-      <c r="A695" s="10"/>
-      <c r="B695" s="10"/>
-      <c r="C695" s="10"/>
-    </row>
-    <row r="696" spans="1:3">
-      <c r="A696" s="10"/>
-      <c r="C696" s="10"/>
-    </row>
-    <row r="697" spans="1:3">
-      <c r="A697" s="10"/>
-      <c r="C697" s="10"/>
-    </row>
-    <row r="698" spans="1:3">
-      <c r="A698" s="10"/>
-      <c r="C698" s="10"/>
-    </row>
-    <row r="699" spans="1:3">
-      <c r="A699" s="10"/>
-      <c r="B699" s="10"/>
-      <c r="C699" s="10"/>
-    </row>
-    <row r="700" spans="1:3">
-      <c r="A700" s="10"/>
-      <c r="C700" s="10"/>
+      <c r="A694" s="10" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B694" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C694" t="s">
+        <v>258</v>
+      </c>
+      <c r="D694" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="695" spans="1:4">
+      <c r="A695" s="10" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B695" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C695" t="s">
+        <v>258</v>
+      </c>
+      <c r="D695" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="696" spans="1:4">
+      <c r="A696" s="10" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B696" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C696" t="s">
+        <v>258</v>
+      </c>
+      <c r="D696" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="697" spans="1:4">
+      <c r="A697" s="10" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B697" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C697" t="s">
+        <v>258</v>
+      </c>
+      <c r="D697" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="698" spans="1:4">
+      <c r="A698" s="10" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B698" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C698" t="s">
+        <v>258</v>
+      </c>
+      <c r="D698" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="699" spans="1:4">
+      <c r="A699" s="10" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B699" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C699" t="s">
+        <v>258</v>
+      </c>
+      <c r="D699" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="700" spans="1:4">
+      <c r="A700" s="10" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B700" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C700" t="s">
+        <v>258</v>
+      </c>
+      <c r="D700" s="2" t="s">
+        <v>1113</v>
+      </c>
     </row>
     <row r="701" spans="1:4">
-      <c r="A701" s="10"/>
-      <c r="B701" s="10"/>
-      <c r="C701" s="10"/>
-      <c r="D701" s="11"/>
+      <c r="A701" s="10" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B701" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C701" t="s">
+        <v>258</v>
+      </c>
+      <c r="D701" s="2" t="s">
+        <v>1113</v>
+      </c>
     </row>
     <row r="702" spans="1:4">
-      <c r="A702" s="10"/>
-      <c r="B702" s="10"/>
-      <c r="C702" s="10"/>
-      <c r="D702" s="11"/>
-    </row>
-    <row r="703" spans="1:3">
-      <c r="A703" s="10"/>
-      <c r="C703" s="10"/>
+      <c r="A702" s="10" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B702" s="10" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C702" t="s">
+        <v>258</v>
+      </c>
+      <c r="D702" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="703" spans="1:4">
+      <c r="A703" s="10" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B703" t="s">
+        <v>324</v>
+      </c>
+      <c r="C703" t="s">
+        <v>258</v>
+      </c>
+      <c r="D703" s="2" t="s">
+        <v>1113</v>
+      </c>
     </row>
     <row r="704" spans="1:4">
-      <c r="A704" s="10"/>
-      <c r="B704" s="10"/>
-      <c r="C704" s="10"/>
-      <c r="D704" s="11"/>
-    </row>
-    <row r="705" spans="1:3">
-      <c r="A705" s="10"/>
-      <c r="C705" s="10"/>
-    </row>
-    <row r="706" spans="1:3">
-      <c r="A706" s="10"/>
-      <c r="B706" s="10"/>
-      <c r="C706" s="10"/>
+      <c r="A704" s="10" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B704" t="s">
+        <v>324</v>
+      </c>
+      <c r="C704" t="s">
+        <v>258</v>
+      </c>
+      <c r="D704" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="705" spans="1:4">
+      <c r="A705" s="10" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B705" t="s">
+        <v>324</v>
+      </c>
+      <c r="C705" t="s">
+        <v>258</v>
+      </c>
+      <c r="D705" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="706" spans="1:4">
+      <c r="A706" s="10" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B706" t="s">
+        <v>324</v>
+      </c>
+      <c r="C706" t="s">
+        <v>258</v>
+      </c>
+      <c r="D706" s="2" t="s">
+        <v>1113</v>
+      </c>
     </row>
     <row r="707" spans="1:4">
-      <c r="A707" s="10"/>
-      <c r="B707" s="10"/>
-      <c r="C707" s="10"/>
-      <c r="D707" s="11"/>
-    </row>
-    <row r="708" spans="2:4">
-      <c r="B708" s="10"/>
-      <c r="C708" s="10"/>
-      <c r="D708" s="11"/>
-    </row>
-    <row r="709" spans="1:3">
-      <c r="A709" s="10"/>
-      <c r="B709" s="10"/>
-      <c r="C709" s="10"/>
-    </row>
-    <row r="710" spans="1:3">
-      <c r="A710" s="10"/>
-      <c r="B710" s="10"/>
-      <c r="C710" s="10"/>
-    </row>
-    <row r="711" spans="1:3">
-      <c r="A711" s="10"/>
-      <c r="C711" s="10"/>
-    </row>
-    <row r="712" spans="1:3">
-      <c r="A712" s="10"/>
-      <c r="C712" s="10"/>
-    </row>
-    <row r="713" spans="1:3">
-      <c r="A713" s="10"/>
-      <c r="C713" s="10"/>
+      <c r="A707" s="10" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B707" t="s">
+        <v>324</v>
+      </c>
+      <c r="C707" t="s">
+        <v>258</v>
+      </c>
+      <c r="D707" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="708" spans="1:4">
+      <c r="A708" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B708" t="s">
+        <v>324</v>
+      </c>
+      <c r="C708" t="s">
+        <v>258</v>
+      </c>
+      <c r="D708" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="709" spans="1:4">
+      <c r="A709" s="10" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B709" s="10" t="s">
+        <v>731</v>
+      </c>
+      <c r="C709" t="s">
+        <v>258</v>
+      </c>
+      <c r="D709" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="710" spans="1:4">
+      <c r="A710" s="10" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B710" t="s">
+        <v>324</v>
+      </c>
+      <c r="C710" t="s">
+        <v>258</v>
+      </c>
+      <c r="D710" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="711" spans="1:4">
+      <c r="A711" s="10" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B711" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C711" t="s">
+        <v>258</v>
+      </c>
+      <c r="D711" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="712" spans="1:4">
+      <c r="A712" s="10" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B712" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C712" t="s">
+        <v>258</v>
+      </c>
+      <c r="D712" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="713" spans="1:4">
+      <c r="A713" s="10" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B713" t="s">
+        <v>464</v>
+      </c>
+      <c r="C713" t="s">
+        <v>258</v>
+      </c>
+      <c r="D713" s="2" t="s">
+        <v>1113</v>
+      </c>
     </row>
     <row r="714" spans="1:4">
-      <c r="A714" s="10"/>
-      <c r="C714" s="10"/>
-      <c r="D714" s="11"/>
+      <c r="A714" s="10" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B714" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C714" t="s">
+        <v>258</v>
+      </c>
+      <c r="D714" s="2" t="s">
+        <v>1113</v>
+      </c>
     </row>
     <row r="715" spans="1:4">
-      <c r="A715" s="10"/>
-      <c r="C715" s="10"/>
-      <c r="D715" s="11"/>
+      <c r="A715" s="10" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B715" t="s">
+        <v>985</v>
+      </c>
+      <c r="C715" t="s">
+        <v>258</v>
+      </c>
+      <c r="D715" s="2" t="s">
+        <v>1113</v>
+      </c>
     </row>
     <row r="716" spans="1:4">
-      <c r="A716" s="10"/>
-      <c r="B716" s="10"/>
-      <c r="C716" s="10"/>
-      <c r="D716" s="11"/>
+      <c r="A716" s="10" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B716" s="10" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C716" t="s">
+        <v>258</v>
+      </c>
+      <c r="D716" s="2" t="s">
+        <v>1113</v>
+      </c>
     </row>
     <row r="717" spans="1:4">
-      <c r="A717" s="10"/>
-      <c r="B717" s="10"/>
-      <c r="C717" s="10"/>
-      <c r="D717" s="11"/>
+      <c r="A717" s="10" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B717" s="10" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C717" t="s">
+        <v>258</v>
+      </c>
+      <c r="D717" s="2" t="s">
+        <v>1113</v>
+      </c>
     </row>
     <row r="718" spans="1:4">
-      <c r="A718" s="10"/>
-      <c r="C718" s="10"/>
-      <c r="D718" s="11"/>
-    </row>
-    <row r="719" spans="2:4">
-      <c r="B719" s="20"/>
-      <c r="C719" s="10"/>
-      <c r="D719" s="11"/>
-    </row>
-    <row r="720" spans="1:3">
-      <c r="A720" s="10"/>
-      <c r="B720" s="10"/>
-      <c r="C720" s="10"/>
-    </row>
-    <row r="721" spans="1:3">
-      <c r="A721" s="10"/>
-      <c r="C721" s="10"/>
-    </row>
-    <row r="722" spans="3:3">
-      <c r="C722" s="10"/>
+      <c r="A718" s="10" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B718" t="s">
+        <v>324</v>
+      </c>
+      <c r="C718" t="s">
+        <v>258</v>
+      </c>
+      <c r="D718" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="719" spans="1:4">
+      <c r="A719" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B719" s="20" t="s">
+        <v>856</v>
+      </c>
+      <c r="C719" t="s">
+        <v>258</v>
+      </c>
+      <c r="D719" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="720" spans="1:4">
+      <c r="A720" s="10" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B720" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="C720" t="s">
+        <v>258</v>
+      </c>
+      <c r="D720" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="721" spans="1:4">
+      <c r="A721" s="10" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B721" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C721" t="s">
+        <v>258</v>
+      </c>
+      <c r="D721" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="722" spans="1:4">
+      <c r="A722" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B722" t="s">
+        <v>324</v>
+      </c>
+      <c r="C722" t="s">
+        <v>258</v>
+      </c>
+      <c r="D722" s="2" t="s">
+        <v>1113</v>
+      </c>
     </row>
     <row r="723" spans="1:4">
-      <c r="A723" s="10"/>
-      <c r="B723" s="10"/>
-      <c r="C723" s="10"/>
-      <c r="D723" s="11"/>
-    </row>
-    <row r="724" spans="1:3">
-      <c r="A724" s="10"/>
-      <c r="C724" s="10"/>
-    </row>
-    <row r="725" spans="1:3">
-      <c r="A725" s="10"/>
-      <c r="C725" s="10"/>
-    </row>
-    <row r="726" spans="1:3">
-      <c r="A726" s="10"/>
-      <c r="C726" s="10"/>
-    </row>
-    <row r="727" spans="1:3">
-      <c r="A727" s="10"/>
-      <c r="B727" s="10"/>
-      <c r="C727" s="10"/>
-    </row>
-    <row r="728" spans="1:3">
-      <c r="A728" s="10"/>
-      <c r="B728" s="21"/>
-      <c r="C728" s="10"/>
-    </row>
-    <row r="729" spans="1:3">
+      <c r="A723" s="10" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B723" s="10" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C723" t="s">
+        <v>258</v>
+      </c>
+      <c r="D723" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="724" spans="1:4">
+      <c r="A724" s="10" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B724" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C724" t="s">
+        <v>258</v>
+      </c>
+      <c r="D724" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="725" spans="1:4">
+      <c r="A725" s="10" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B725" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C725" t="s">
+        <v>258</v>
+      </c>
+      <c r="D725" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="726" spans="1:4">
+      <c r="A726" s="10" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B726" t="s">
+        <v>263</v>
+      </c>
+      <c r="C726" t="s">
+        <v>258</v>
+      </c>
+      <c r="D726" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="727" spans="1:4">
+      <c r="A727" s="10" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B727" t="s">
+        <v>263</v>
+      </c>
+      <c r="C727" t="s">
+        <v>258</v>
+      </c>
+      <c r="D727" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="728" spans="1:4">
+      <c r="A728" s="10" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B728" s="21" t="s">
+        <v>285</v>
+      </c>
+      <c r="C728" t="s">
+        <v>258</v>
+      </c>
+      <c r="D728" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="729" spans="1:4">
       <c r="A729" s="10"/>
       <c r="C729" s="10"/>
     </row>
-    <row r="730" spans="1:3">
+    <row r="730" spans="1:4">
       <c r="A730" s="10"/>
       <c r="C730" s="10"/>
     </row>
-    <row r="731" spans="1:3">
+    <row r="731" spans="1:4">
       <c r="A731" s="10"/>
       <c r="C731" s="10"/>
     </row>
@@ -13256,25 +13873,25 @@
       <c r="C732" s="10"/>
       <c r="D732" s="11"/>
     </row>
-    <row r="733" spans="1:3">
+    <row r="733" spans="1:4">
       <c r="A733" s="10"/>
       <c r="B733" s="10"/>
       <c r="C733" s="10"/>
     </row>
-    <row r="734" spans="1:3">
+    <row r="734" spans="1:4">
       <c r="A734" s="10"/>
       <c r="C734" s="10"/>
     </row>
-    <row r="735" spans="1:3">
+    <row r="735" spans="1:4">
       <c r="A735" s="10"/>
       <c r="C735" s="10"/>
     </row>
-    <row r="736" spans="1:3">
+    <row r="736" spans="1:4">
       <c r="A736" s="10"/>
       <c r="B736" s="10"/>
       <c r="C736" s="10"/>
     </row>
-    <row r="737" spans="3:3">
+    <row r="737" spans="1:4">
       <c r="C737" s="10"/>
     </row>
     <row r="738" spans="1:4">
@@ -13289,17 +13906,17 @@
       <c r="C739" s="10"/>
       <c r="D739" s="11"/>
     </row>
-    <row r="740" spans="1:3">
+    <row r="740" spans="1:4">
       <c r="A740" s="10"/>
       <c r="B740" s="10"/>
       <c r="C740" s="10"/>
     </row>
-    <row r="741" spans="1:3">
+    <row r="741" spans="1:4">
       <c r="A741" s="10"/>
       <c r="B741" s="10"/>
       <c r="C741" s="10"/>
     </row>
-    <row r="742" spans="1:3">
+    <row r="742" spans="1:4">
       <c r="A742" s="10"/>
       <c r="B742" s="10"/>
       <c r="C742" s="10"/>
@@ -13310,7 +13927,7 @@
       <c r="C743" s="10"/>
       <c r="D743" s="11"/>
     </row>
-    <row r="744" spans="1:3">
+    <row r="744" spans="1:4">
       <c r="A744" s="10"/>
       <c r="C744" s="10"/>
     </row>
@@ -13326,7 +13943,7 @@
       <c r="C746" s="10"/>
       <c r="D746" s="11"/>
     </row>
-    <row r="747" spans="1:3">
+    <row r="747" spans="1:4">
       <c r="A747" s="10"/>
       <c r="B747" s="10"/>
       <c r="C747" s="10"/>
@@ -13337,48 +13954,48 @@
       <c r="C748" s="10"/>
       <c r="D748" s="11"/>
     </row>
-    <row r="749" spans="1:3">
+    <row r="749" spans="1:4">
       <c r="A749" s="10"/>
       <c r="B749" s="10"/>
       <c r="C749" s="10"/>
     </row>
-    <row r="750" spans="1:3">
+    <row r="750" spans="1:4">
       <c r="A750" s="10"/>
       <c r="B750" s="10"/>
       <c r="C750" s="10"/>
     </row>
-    <row r="751" spans="1:3">
+    <row r="751" spans="1:4">
       <c r="A751" s="10"/>
       <c r="C751" s="10"/>
     </row>
-    <row r="752" spans="1:3">
+    <row r="752" spans="1:4">
       <c r="A752" s="10"/>
       <c r="C752" s="10"/>
     </row>
-    <row r="753" spans="1:3">
+    <row r="753" spans="1:4">
       <c r="A753" s="10"/>
       <c r="C753" s="10"/>
     </row>
-    <row r="754" spans="1:3">
+    <row r="754" spans="1:4">
       <c r="A754" s="10"/>
       <c r="C754" s="10"/>
     </row>
-    <row r="755" spans="1:3">
+    <row r="755" spans="1:4">
       <c r="A755" s="10"/>
       <c r="B755" s="10"/>
       <c r="C755" s="10"/>
     </row>
-    <row r="756" spans="1:3">
+    <row r="756" spans="1:4">
       <c r="A756" s="10"/>
       <c r="B756" s="10"/>
       <c r="C756" s="10"/>
     </row>
-    <row r="757" spans="1:3">
+    <row r="757" spans="1:4">
       <c r="A757" s="10"/>
       <c r="B757" s="10"/>
       <c r="C757" s="10"/>
     </row>
-    <row r="758" spans="1:3">
+    <row r="758" spans="1:4">
       <c r="A758" s="10"/>
       <c r="B758" s="10"/>
       <c r="C758" s="10"/>
@@ -13389,10 +14006,10 @@
       <c r="C759" s="10"/>
       <c r="D759" s="11"/>
     </row>
-    <row r="761" spans="3:3">
+    <row r="761" spans="1:4">
       <c r="C761" s="10"/>
     </row>
-    <row r="762" spans="1:3">
+    <row r="762" spans="1:4">
       <c r="A762" s="10"/>
       <c r="B762" s="10"/>
       <c r="C762" s="10"/>
@@ -13403,12 +14020,12 @@
       <c r="C763" s="10"/>
       <c r="D763" s="11"/>
     </row>
-    <row r="764" spans="1:3">
+    <row r="764" spans="1:4">
       <c r="A764" s="10"/>
       <c r="B764" s="10"/>
       <c r="C764" s="10"/>
     </row>
-    <row r="765" spans="1:3">
+    <row r="765" spans="1:4">
       <c r="A765" s="10"/>
       <c r="B765" s="10"/>
       <c r="C765" s="10"/>
@@ -13430,7 +14047,7 @@
       <c r="C768" s="10"/>
       <c r="D768" s="11"/>
     </row>
-    <row r="769" spans="1:3">
+    <row r="769" spans="1:4">
       <c r="A769" s="10"/>
       <c r="C769" s="10"/>
     </row>
@@ -13440,11 +14057,11 @@
       <c r="C770" s="10"/>
       <c r="D770" s="11"/>
     </row>
-    <row r="771" spans="1:3">
+    <row r="771" spans="1:4">
       <c r="A771" s="10"/>
       <c r="C771" s="10"/>
     </row>
-    <row r="772" spans="1:3">
+    <row r="772" spans="1:4">
       <c r="A772" s="10"/>
       <c r="C772" s="10"/>
     </row>
@@ -13488,12 +14105,12 @@
       <c r="C779" s="10"/>
       <c r="D779" s="11"/>
     </row>
-    <row r="780" spans="1:3">
+    <row r="780" spans="1:4">
       <c r="A780" s="10"/>
       <c r="B780" s="10"/>
       <c r="C780" s="10"/>
     </row>
-    <row r="781" spans="1:3">
+    <row r="781" spans="1:4">
       <c r="A781" s="10"/>
       <c r="B781" s="10"/>
       <c r="C781" s="10"/>
@@ -13514,16 +14131,16 @@
       <c r="C784" s="10"/>
       <c r="D784" s="11"/>
     </row>
-    <row r="785" spans="1:3">
+    <row r="785" spans="1:4">
       <c r="A785" s="10"/>
       <c r="B785" s="22"/>
       <c r="C785" s="10"/>
     </row>
-    <row r="786" spans="1:3">
+    <row r="786" spans="1:4">
       <c r="A786" s="10"/>
       <c r="C786" s="10"/>
     </row>
-    <row r="787" spans="3:3">
+    <row r="787" spans="1:4">
       <c r="C787" s="10"/>
     </row>
     <row r="788" spans="1:4">
@@ -13531,12 +14148,12 @@
       <c r="C788" s="10"/>
       <c r="D788" s="11"/>
     </row>
-    <row r="789" spans="1:3">
+    <row r="789" spans="1:4">
       <c r="A789" s="10"/>
       <c r="B789" s="10"/>
       <c r="C789" s="10"/>
     </row>
-    <row r="790" spans="2:3">
+    <row r="790" spans="1:4">
       <c r="B790" s="10"/>
       <c r="C790" s="10"/>
     </row>
@@ -13545,16 +14162,16 @@
       <c r="C791" s="10"/>
       <c r="D791" s="11"/>
     </row>
-    <row r="792" spans="1:3">
+    <row r="792" spans="1:4">
       <c r="A792" s="10"/>
       <c r="B792" s="10"/>
       <c r="C792" s="10"/>
     </row>
-    <row r="793" spans="2:3">
+    <row r="793" spans="1:4">
       <c r="B793" s="10"/>
       <c r="C793" s="10"/>
     </row>
-    <row r="794" spans="1:3">
+    <row r="794" spans="1:4">
       <c r="A794" s="10"/>
       <c r="C794" s="10"/>
     </row>
@@ -13570,7 +14187,7 @@
       <c r="C796" s="10"/>
       <c r="D796" s="11"/>
     </row>
-    <row r="797" spans="1:3">
+    <row r="797" spans="1:4">
       <c r="A797" s="10"/>
       <c r="C797" s="10"/>
     </row>
@@ -13580,43 +14197,43 @@
       <c r="C798" s="10"/>
       <c r="D798" s="11"/>
     </row>
-    <row r="799" spans="1:3">
+    <row r="799" spans="1:4">
       <c r="A799" s="10"/>
       <c r="B799" s="23"/>
       <c r="C799" s="10"/>
     </row>
-    <row r="800" spans="1:3">
+    <row r="800" spans="1:4">
       <c r="A800" s="10"/>
       <c r="C800" s="10"/>
     </row>
-    <row r="801" spans="1:3">
+    <row r="801" spans="1:4">
       <c r="A801" s="10"/>
       <c r="C801" s="10"/>
     </row>
-    <row r="802" spans="1:3">
+    <row r="802" spans="1:4">
       <c r="A802" s="10"/>
       <c r="C802" s="10"/>
     </row>
-    <row r="803" spans="1:3">
+    <row r="803" spans="1:4">
       <c r="A803" s="10"/>
       <c r="B803" s="10"/>
       <c r="C803" s="10"/>
     </row>
-    <row r="804" spans="1:3">
+    <row r="804" spans="1:4">
       <c r="A804" s="10"/>
       <c r="C804" s="10"/>
     </row>
-    <row r="805" spans="1:3">
+    <row r="805" spans="1:4">
       <c r="A805" s="10"/>
       <c r="B805" s="10"/>
       <c r="C805" s="10"/>
     </row>
-    <row r="806" spans="1:3">
+    <row r="806" spans="1:4">
       <c r="A806" s="10"/>
       <c r="B806" s="10"/>
       <c r="C806" s="10"/>
     </row>
-    <row r="807" spans="1:3">
+    <row r="807" spans="1:4">
       <c r="A807" s="10"/>
       <c r="B807" s="10"/>
       <c r="C807" s="10"/>
@@ -13627,7 +14244,7 @@
       <c r="C808" s="10"/>
       <c r="D808" s="11"/>
     </row>
-    <row r="809" spans="1:3">
+    <row r="809" spans="1:4">
       <c r="A809" s="10"/>
       <c r="C809" s="10"/>
     </row>
@@ -13637,7 +14254,7 @@
       <c r="C810" s="10"/>
       <c r="D810" s="11"/>
     </row>
-    <row r="811" spans="1:3">
+    <row r="811" spans="1:4">
       <c r="A811" s="10"/>
       <c r="B811" s="10"/>
       <c r="C811" s="10"/>
@@ -13648,25 +14265,25 @@
       <c r="C812" s="10"/>
       <c r="D812" s="11"/>
     </row>
-    <row r="813" spans="1:3">
+    <row r="813" spans="1:4">
       <c r="A813" s="10"/>
       <c r="B813" s="10"/>
       <c r="C813" s="10"/>
     </row>
-    <row r="814" spans="1:3">
+    <row r="814" spans="1:4">
       <c r="A814" s="10"/>
       <c r="C814" s="10"/>
     </row>
-    <row r="815" spans="1:3">
+    <row r="815" spans="1:4">
       <c r="A815" s="10"/>
       <c r="B815" s="10"/>
       <c r="C815" s="10"/>
     </row>
-    <row r="816" spans="1:3">
+    <row r="816" spans="1:4">
       <c r="A816" s="10"/>
       <c r="C816" s="10"/>
     </row>
-    <row r="817" spans="1:3">
+    <row r="817" spans="1:4">
       <c r="A817" s="10"/>
       <c r="C817" s="10"/>
     </row>
@@ -13676,12 +14293,12 @@
       <c r="C818" s="10"/>
       <c r="D818" s="11"/>
     </row>
-    <row r="819" spans="1:3">
+    <row r="819" spans="1:4">
       <c r="A819" s="10"/>
       <c r="B819" s="10"/>
       <c r="C819" s="10"/>
     </row>
-    <row r="820" spans="1:3">
+    <row r="820" spans="1:4">
       <c r="A820" s="10"/>
       <c r="C820" s="10"/>
     </row>
@@ -13691,26 +14308,26 @@
       <c r="C821" s="10"/>
       <c r="D821" s="11"/>
     </row>
-    <row r="822" spans="1:3">
+    <row r="822" spans="1:4">
       <c r="A822" s="10"/>
       <c r="B822" s="10"/>
       <c r="C822" s="10"/>
     </row>
-    <row r="823" spans="1:3">
+    <row r="823" spans="1:4">
       <c r="A823" s="10"/>
       <c r="B823" s="10"/>
       <c r="C823" s="10"/>
     </row>
-    <row r="824" spans="1:3">
+    <row r="824" spans="1:4">
       <c r="A824" s="10"/>
       <c r="C824" s="10"/>
     </row>
-    <row r="825" spans="1:3">
+    <row r="825" spans="1:4">
       <c r="A825" s="10"/>
       <c r="B825" s="10"/>
       <c r="C825" s="10"/>
     </row>
-    <row r="826" spans="1:3">
+    <row r="826" spans="1:4">
       <c r="A826" s="10"/>
       <c r="B826" s="10"/>
       <c r="C826" s="10"/>
@@ -13768,16 +14385,16 @@
       <c r="C835" s="10"/>
       <c r="D835" s="11"/>
     </row>
-    <row r="836" spans="1:3">
+    <row r="836" spans="1:4">
       <c r="A836" s="10"/>
       <c r="B836" s="10"/>
       <c r="C836" s="10"/>
     </row>
-    <row r="837" spans="1:3">
+    <row r="837" spans="1:4">
       <c r="A837" s="10"/>
       <c r="C837" s="10"/>
     </row>
-    <row r="838" spans="1:3">
+    <row r="838" spans="1:4">
       <c r="A838" s="10"/>
       <c r="C838" s="10"/>
     </row>
@@ -13786,16 +14403,16 @@
       <c r="C839" s="10"/>
       <c r="D839" s="11"/>
     </row>
-    <row r="840" spans="1:3">
+    <row r="840" spans="1:4">
       <c r="A840" s="10"/>
       <c r="C840" s="10"/>
     </row>
-    <row r="841" spans="1:3">
+    <row r="841" spans="1:4">
       <c r="A841" s="10"/>
       <c r="B841" s="10"/>
       <c r="C841" s="10"/>
     </row>
-    <row r="842" spans="1:3">
+    <row r="842" spans="1:4">
       <c r="A842" s="10"/>
       <c r="C842" s="10"/>
     </row>
@@ -13805,16 +14422,16 @@
       <c r="C843" s="10"/>
       <c r="D843" s="11"/>
     </row>
-    <row r="844" spans="1:3">
+    <row r="844" spans="1:4">
       <c r="A844" s="10"/>
       <c r="B844" s="10"/>
       <c r="C844" s="10"/>
     </row>
-    <row r="845" spans="2:3">
+    <row r="845" spans="1:4">
       <c r="B845" s="10"/>
       <c r="C845" s="10"/>
     </row>
-    <row r="846" spans="1:3">
+    <row r="846" spans="1:4">
       <c r="A846" s="10"/>
       <c r="B846" s="10"/>
       <c r="C846" s="10"/>
@@ -13829,7 +14446,7 @@
       <c r="C848" s="10"/>
       <c r="D848" s="11"/>
     </row>
-    <row r="849" spans="1:3">
+    <row r="849" spans="1:4">
       <c r="A849" s="10"/>
       <c r="B849" s="10"/>
       <c r="C849" s="10"/>
@@ -13839,16 +14456,16 @@
       <c r="C850" s="10"/>
       <c r="D850" s="11"/>
     </row>
-    <row r="851" spans="1:3">
+    <row r="851" spans="1:4">
       <c r="A851" s="10"/>
       <c r="B851" s="10"/>
       <c r="C851" s="10"/>
     </row>
-    <row r="852" spans="1:3">
+    <row r="852" spans="1:4">
       <c r="A852" s="10"/>
       <c r="C852" s="10"/>
     </row>
-    <row r="853" spans="1:3">
+    <row r="853" spans="1:4">
       <c r="A853" s="10"/>
       <c r="C853" s="10"/>
     </row>
@@ -13862,11 +14479,11 @@
       <c r="C855" s="10"/>
       <c r="D855" s="11"/>
     </row>
-    <row r="856" spans="1:3">
+    <row r="856" spans="1:4">
       <c r="A856" s="10"/>
       <c r="C856" s="10"/>
     </row>
-    <row r="857" spans="1:3">
+    <row r="857" spans="1:4">
       <c r="A857" s="10"/>
       <c r="C857" s="10"/>
     </row>
@@ -13876,12 +14493,12 @@
       <c r="C858" s="10"/>
       <c r="D858" s="11"/>
     </row>
-    <row r="859" spans="1:3">
+    <row r="859" spans="1:4">
       <c r="A859" s="10"/>
       <c r="B859" s="10"/>
       <c r="C859" s="10"/>
     </row>
-    <row r="860" spans="1:3">
+    <row r="860" spans="1:4">
       <c r="A860" s="10"/>
       <c r="C860" s="10"/>
     </row>
@@ -13903,23 +14520,23 @@
       <c r="C863" s="10"/>
       <c r="D863" s="11"/>
     </row>
-    <row r="864" spans="1:3">
+    <row r="864" spans="1:4">
       <c r="A864" s="10"/>
       <c r="C864" s="10"/>
     </row>
-    <row r="865" spans="1:3">
+    <row r="865" spans="1:4">
       <c r="A865" s="10"/>
       <c r="C865" s="10"/>
     </row>
-    <row r="866" spans="1:3">
+    <row r="866" spans="1:4">
       <c r="A866" s="10"/>
       <c r="C866" s="10"/>
     </row>
-    <row r="867" spans="1:3">
+    <row r="867" spans="1:4">
       <c r="A867" s="10"/>
       <c r="C867" s="10"/>
     </row>
-    <row r="868" spans="1:3">
+    <row r="868" spans="1:4">
       <c r="A868" s="10"/>
       <c r="B868" s="10"/>
       <c r="C868" s="10"/>
@@ -13929,24 +14546,24 @@
       <c r="C869" s="10"/>
       <c r="D869" s="11"/>
     </row>
-    <row r="870" spans="1:3">
+    <row r="870" spans="1:4">
       <c r="A870" s="10"/>
       <c r="C870" s="10"/>
     </row>
-    <row r="871" spans="1:3">
+    <row r="871" spans="1:4">
       <c r="A871" s="10"/>
       <c r="B871" s="24"/>
       <c r="C871" s="10"/>
     </row>
-    <row r="872" spans="1:3">
+    <row r="872" spans="1:4">
       <c r="A872" s="10"/>
       <c r="C872" s="10"/>
     </row>
-    <row r="873" spans="1:3">
+    <row r="873" spans="1:4">
       <c r="A873" s="10"/>
       <c r="C873" s="10"/>
     </row>
-    <row r="874" spans="1:3">
+    <row r="874" spans="1:4">
       <c r="A874" s="10"/>
       <c r="B874" s="10"/>
       <c r="C874" s="10"/>
@@ -13963,7 +14580,7 @@
       <c r="C876" s="10"/>
       <c r="D876" s="11"/>
     </row>
-    <row r="877" spans="1:3">
+    <row r="877" spans="1:4">
       <c r="A877" s="10"/>
       <c r="C877" s="10"/>
     </row>
@@ -13973,15 +14590,15 @@
       <c r="C878" s="10"/>
       <c r="D878" s="11"/>
     </row>
-    <row r="879" spans="1:3">
+    <row r="879" spans="1:4">
       <c r="A879" s="10"/>
       <c r="C879" s="10"/>
     </row>
-    <row r="880" spans="1:3">
+    <row r="880" spans="1:4">
       <c r="A880" s="10"/>
       <c r="C880" s="10"/>
     </row>
-    <row r="881" spans="1:3">
+    <row r="881" spans="1:4">
       <c r="A881" s="10"/>
       <c r="C881" s="10"/>
     </row>
@@ -13990,40 +14607,40 @@
       <c r="C882" s="10"/>
       <c r="D882" s="11"/>
     </row>
-    <row r="883" spans="1:3">
+    <row r="883" spans="1:4">
       <c r="A883" s="10"/>
       <c r="B883" s="10"/>
       <c r="C883" s="10"/>
     </row>
-    <row r="884" spans="1:3">
+    <row r="884" spans="1:4">
       <c r="A884" s="10"/>
       <c r="B884" s="10"/>
       <c r="C884" s="10"/>
     </row>
-    <row r="885" spans="1:3">
+    <row r="885" spans="1:4">
       <c r="A885" s="10"/>
       <c r="B885" s="10"/>
       <c r="C885" s="10"/>
     </row>
-    <row r="886" spans="1:3">
+    <row r="886" spans="1:4">
       <c r="A886" s="10"/>
       <c r="B886" s="10"/>
       <c r="C886" s="10"/>
     </row>
-    <row r="887" spans="1:3">
+    <row r="887" spans="1:4">
       <c r="A887" s="10"/>
       <c r="B887" s="10"/>
       <c r="C887" s="10"/>
     </row>
-    <row r="888" spans="1:3">
+    <row r="888" spans="1:4">
       <c r="A888" s="10"/>
       <c r="C888" s="10"/>
     </row>
-    <row r="889" spans="1:3">
+    <row r="889" spans="1:4">
       <c r="A889" s="10"/>
       <c r="C889" s="10"/>
     </row>
-    <row r="890" spans="1:3">
+    <row r="890" spans="1:4">
       <c r="A890" s="10"/>
       <c r="B890" s="22"/>
       <c r="C890" s="10"/>
@@ -14033,17 +14650,17 @@
       <c r="C891" s="10"/>
       <c r="D891" s="11"/>
     </row>
-    <row r="892" spans="1:3">
+    <row r="892" spans="1:4">
       <c r="A892" s="10"/>
       <c r="B892" s="10"/>
       <c r="C892" s="10"/>
     </row>
-    <row r="893" spans="1:3">
+    <row r="893" spans="1:4">
       <c r="A893" s="10"/>
       <c r="B893" s="10"/>
       <c r="C893" s="10"/>
     </row>
-    <row r="894" spans="1:3">
+    <row r="894" spans="1:4">
       <c r="A894" s="10"/>
       <c r="B894" s="10"/>
       <c r="C894" s="10"/>
@@ -14071,17 +14688,17 @@
       <c r="C898" s="10"/>
       <c r="D898" s="11"/>
     </row>
-    <row r="899" spans="1:3">
+    <row r="899" spans="1:4">
       <c r="A899" s="10"/>
       <c r="B899" s="10"/>
       <c r="C899" s="10"/>
     </row>
-    <row r="900" spans="1:3">
+    <row r="900" spans="1:4">
       <c r="A900" s="10"/>
       <c r="B900" s="10"/>
       <c r="C900" s="10"/>
     </row>
-    <row r="901" spans="1:3">
+    <row r="901" spans="1:4">
       <c r="A901" s="10"/>
       <c r="B901" s="10"/>
       <c r="C901" s="10"/>
@@ -14092,12 +14709,12 @@
       <c r="C902" s="10"/>
       <c r="D902" s="11"/>
     </row>
-    <row r="903" spans="1:3">
+    <row r="903" spans="1:4">
       <c r="A903" s="10"/>
       <c r="B903" s="10"/>
       <c r="C903" s="10"/>
     </row>
-    <row r="904" spans="2:4">
+    <row r="904" spans="1:4">
       <c r="B904" s="10"/>
       <c r="C904" s="10"/>
       <c r="D904" s="11"/>
@@ -14108,12 +14725,12 @@
       <c r="C905" s="10"/>
       <c r="D905" s="11"/>
     </row>
-    <row r="906" spans="2:4">
+    <row r="906" spans="1:4">
       <c r="B906" s="10"/>
       <c r="C906" s="10"/>
       <c r="D906" s="11"/>
     </row>
-    <row r="907" spans="1:3">
+    <row r="907" spans="1:4">
       <c r="A907" s="10"/>
       <c r="C907" s="10"/>
     </row>
@@ -14123,7 +14740,7 @@
       <c r="C908" s="10"/>
       <c r="D908" s="27"/>
     </row>
-    <row r="909" spans="1:3">
+    <row r="909" spans="1:4">
       <c r="A909" s="10"/>
       <c r="B909" s="10"/>
       <c r="C909" s="10"/>
@@ -14140,7 +14757,7 @@
       <c r="C911" s="10"/>
       <c r="D911" s="11"/>
     </row>
-    <row r="912" spans="2:3">
+    <row r="912" spans="1:4">
       <c r="B912" s="10"/>
       <c r="C912" s="10"/>
     </row>
@@ -14168,7 +14785,7 @@
       <c r="C916" s="10"/>
       <c r="D916" s="30"/>
     </row>
-    <row r="917" spans="1:3">
+    <row r="917" spans="1:4">
       <c r="A917" s="10"/>
       <c r="B917" s="10"/>
       <c r="C917" s="10"/>
@@ -14179,10 +14796,10 @@
       <c r="C918" s="10"/>
       <c r="D918" s="11"/>
     </row>
-    <row r="919" spans="3:3">
+    <row r="919" spans="1:4">
       <c r="C919" s="10"/>
     </row>
-    <row r="920" spans="2:4">
+    <row r="920" spans="1:4">
       <c r="B920" s="10"/>
       <c r="C920" s="10"/>
       <c r="D920" s="27"/>
@@ -14193,27 +14810,27 @@
       <c r="C922" s="10"/>
       <c r="D922" s="11"/>
     </row>
-    <row r="923" spans="1:3">
+    <row r="923" spans="1:4">
       <c r="A923" s="10"/>
       <c r="B923" s="10"/>
       <c r="C923" s="10"/>
     </row>
-    <row r="924" spans="1:3">
+    <row r="924" spans="1:4">
       <c r="A924" s="10"/>
       <c r="B924" s="10"/>
       <c r="C924" s="10"/>
     </row>
-    <row r="925" spans="1:3">
+    <row r="925" spans="1:4">
       <c r="A925" s="10"/>
       <c r="B925" s="10"/>
       <c r="C925" s="10"/>
     </row>
-    <row r="926" spans="1:3">
+    <row r="926" spans="1:4">
       <c r="A926" s="10"/>
       <c r="B926" s="10"/>
       <c r="C926" s="10"/>
     </row>
-    <row r="927" spans="2:3">
+    <row r="927" spans="1:4">
       <c r="B927" s="31"/>
       <c r="C927" s="10"/>
     </row>
@@ -14223,7 +14840,7 @@
       <c r="C928" s="10"/>
       <c r="D928" s="11"/>
     </row>
-    <row r="930" spans="1:3">
+    <row r="930" spans="1:4">
       <c r="A930" s="10"/>
       <c r="B930" s="10"/>
       <c r="C930" s="10"/>
@@ -14240,7 +14857,7 @@
       <c r="C932" s="10"/>
       <c r="D932" s="11"/>
     </row>
-    <row r="933" spans="1:3">
+    <row r="933" spans="1:4">
       <c r="A933" s="10"/>
       <c r="B933" s="10"/>
       <c r="C933" s="10"/>
@@ -14255,35 +14872,35 @@
       <c r="C935" s="10"/>
       <c r="D935" s="11"/>
     </row>
-    <row r="936" spans="2:4">
+    <row r="936" spans="1:4">
       <c r="B936" s="10"/>
       <c r="C936" s="10"/>
       <c r="D936" s="27"/>
     </row>
-    <row r="937" spans="2:3">
+    <row r="937" spans="1:4">
       <c r="B937" s="10"/>
       <c r="C937" s="10"/>
     </row>
-    <row r="938" spans="1:3">
+    <row r="938" spans="1:4">
       <c r="A938" s="10"/>
       <c r="B938" s="10"/>
       <c r="C938" s="10"/>
     </row>
-    <row r="939" spans="1:3">
+    <row r="939" spans="1:4">
       <c r="A939" s="10"/>
       <c r="B939" s="10"/>
       <c r="C939" s="10"/>
     </row>
-    <row r="940" spans="1:3">
+    <row r="940" spans="1:4">
       <c r="A940" s="10"/>
       <c r="C940" s="10"/>
     </row>
-    <row r="941" spans="1:3">
+    <row r="941" spans="1:4">
       <c r="A941" s="10"/>
       <c r="B941" s="10"/>
       <c r="C941" s="10"/>
     </row>
-    <row r="942" spans="1:3">
+    <row r="942" spans="1:4">
       <c r="A942" s="10"/>
       <c r="B942" s="10"/>
       <c r="C942" s="10"/>
@@ -14294,7 +14911,7 @@
       <c r="C943" s="10"/>
       <c r="D943" s="11"/>
     </row>
-    <row r="944" spans="1:3">
+    <row r="944" spans="1:4">
       <c r="A944" s="10"/>
       <c r="B944" s="10"/>
       <c r="C944" s="10"/>
@@ -14313,12 +14930,12 @@
       <c r="C947" s="10"/>
       <c r="D947" s="11"/>
     </row>
-    <row r="948" spans="1:3">
+    <row r="948" spans="1:4">
       <c r="A948" s="10"/>
       <c r="B948" s="10"/>
       <c r="C948" s="10"/>
     </row>
-    <row r="949" spans="2:3">
+    <row r="949" spans="1:4">
       <c r="B949" s="32"/>
       <c r="C949" s="10"/>
     </row>
@@ -14328,35 +14945,35 @@
       <c r="C950" s="10"/>
       <c r="D950" s="11"/>
     </row>
-    <row r="951" spans="1:3">
+    <row r="951" spans="1:4">
       <c r="A951" s="10"/>
       <c r="B951" s="10"/>
       <c r="C951" s="10"/>
     </row>
-    <row r="952" spans="2:4">
+    <row r="952" spans="1:4">
       <c r="B952" s="10"/>
       <c r="C952" s="10"/>
       <c r="D952" s="11"/>
     </row>
-    <row r="953" spans="2:3">
+    <row r="953" spans="1:4">
       <c r="B953" s="10"/>
       <c r="C953" s="10"/>
     </row>
-    <row r="954" spans="3:4">
+    <row r="954" spans="1:4">
       <c r="C954" s="10"/>
       <c r="D954" s="11"/>
     </row>
-    <row r="955" spans="1:3">
+    <row r="955" spans="1:4">
       <c r="A955" s="10"/>
       <c r="B955" s="10"/>
       <c r="C955" s="10"/>
     </row>
-    <row r="956" spans="1:3">
+    <row r="956" spans="1:4">
       <c r="A956" s="29"/>
       <c r="B956" s="10"/>
       <c r="C956" s="10"/>
     </row>
-    <row r="957" spans="2:3">
+    <row r="957" spans="1:4">
       <c r="B957" s="10"/>
       <c r="C957" s="10"/>
     </row>
@@ -14366,7 +14983,7 @@
       <c r="C958" s="10"/>
       <c r="D958" s="11"/>
     </row>
-    <row r="959" spans="1:3">
+    <row r="959" spans="1:4">
       <c r="A959" s="10"/>
       <c r="B959" s="10"/>
       <c r="C959" s="10"/>
@@ -14389,7 +15006,7 @@
       <c r="C962" s="10"/>
       <c r="D962" s="11"/>
     </row>
-    <row r="963" spans="1:3">
+    <row r="963" spans="1:4">
       <c r="A963" s="10"/>
       <c r="C963" s="10"/>
     </row>
@@ -14405,10 +15022,10 @@
       <c r="C965" s="10"/>
       <c r="D965" s="11"/>
     </row>
-    <row r="966" spans="1:1">
+    <row r="966" spans="1:4">
       <c r="A966" s="10"/>
     </row>
-    <row r="967" spans="1:3">
+    <row r="967" spans="1:4">
       <c r="A967" s="10"/>
       <c r="B967" s="33"/>
       <c r="C967" s="10"/>
@@ -14431,15 +15048,15 @@
       <c r="C970" s="10"/>
       <c r="D970" s="11"/>
     </row>
-    <row r="971" spans="3:3">
+    <row r="971" spans="1:4">
       <c r="C971" s="10"/>
     </row>
-    <row r="972" spans="2:4">
+    <row r="972" spans="1:4">
       <c r="B972" s="10"/>
       <c r="C972" s="10"/>
       <c r="D972" s="11"/>
     </row>
-    <row r="973" spans="2:3">
+    <row r="973" spans="1:4">
       <c r="B973" s="10"/>
       <c r="C973" s="10"/>
     </row>
@@ -14449,41 +15066,41 @@
       <c r="C974" s="10"/>
       <c r="D974" s="11"/>
     </row>
-    <row r="975" spans="3:3">
+    <row r="975" spans="1:4">
       <c r="C975" s="10"/>
     </row>
-    <row r="976" spans="1:3">
+    <row r="976" spans="1:4">
       <c r="A976" s="10"/>
       <c r="B976" s="10"/>
       <c r="C976" s="10"/>
     </row>
-    <row r="977" spans="1:3">
+    <row r="977" spans="1:4">
       <c r="A977" s="10"/>
       <c r="C977" s="10"/>
     </row>
-    <row r="978" spans="1:3">
+    <row r="978" spans="1:4">
       <c r="A978" s="10"/>
       <c r="B978" s="10"/>
       <c r="C978" s="10"/>
     </row>
-    <row r="979" spans="1:3">
+    <row r="979" spans="1:4">
       <c r="A979" s="10"/>
       <c r="B979" s="10"/>
       <c r="C979" s="10"/>
     </row>
-    <row r="980" spans="2:4">
+    <row r="980" spans="1:4">
       <c r="B980" s="10"/>
       <c r="C980" s="10"/>
       <c r="D980" s="11"/>
     </row>
-    <row r="981" spans="1:1">
+    <row r="981" spans="1:4">
       <c r="A981" s="10"/>
     </row>
-    <row r="982" spans="1:3">
+    <row r="982" spans="1:4">
       <c r="A982" s="10"/>
       <c r="C982" s="10"/>
     </row>
-    <row r="983" spans="2:4">
+    <row r="983" spans="1:4">
       <c r="B983" s="10"/>
       <c r="C983" s="10"/>
       <c r="D983" s="11"/>
@@ -14509,11 +15126,11 @@
       <c r="C987" s="10"/>
       <c r="D987" s="11"/>
     </row>
-    <row r="988" spans="1:3">
+    <row r="988" spans="1:4">
       <c r="A988" s="10"/>
       <c r="C988" s="10"/>
     </row>
-    <row r="989" spans="1:3">
+    <row r="989" spans="1:4">
       <c r="A989" s="10"/>
       <c r="B989" s="10"/>
       <c r="C989" s="10"/>
@@ -14524,7 +15141,7 @@
       <c r="C990" s="10"/>
       <c r="D990" s="11"/>
     </row>
-    <row r="991" spans="3:3">
+    <row r="991" spans="1:4">
       <c r="C991" s="10"/>
     </row>
     <row r="992" spans="1:4">
@@ -14533,12 +15150,12 @@
       <c r="C992" s="10"/>
       <c r="D992" s="11"/>
     </row>
-    <row r="993" spans="2:4">
+    <row r="993" spans="1:4">
       <c r="B993" s="36"/>
       <c r="C993" s="10"/>
       <c r="D993" s="27"/>
     </row>
-    <row r="994" spans="1:3">
+    <row r="994" spans="1:4">
       <c r="A994" s="10"/>
       <c r="B994" s="10"/>
       <c r="C994" s="10"/>
@@ -14561,7 +15178,7 @@
       <c r="C997" s="10"/>
       <c r="D997" s="11"/>
     </row>
-    <row r="998" spans="1:3">
+    <row r="998" spans="1:4">
       <c r="A998" s="10"/>
       <c r="C998" s="10"/>
     </row>
@@ -14571,7 +15188,7 @@
       <c r="C999" s="10"/>
       <c r="D999" s="11"/>
     </row>
-    <row r="1001" spans="2:3">
+    <row r="1001" spans="1:4">
       <c r="B1001" s="10"/>
       <c r="C1001" s="10"/>
     </row>
@@ -14581,7 +15198,7 @@
       <c r="C1002" s="10"/>
       <c r="D1002" s="11"/>
     </row>
-    <row r="1003" spans="1:3">
+    <row r="1003" spans="1:4">
       <c r="A1003" s="10"/>
       <c r="C1003" s="10"/>
     </row>
@@ -14591,10 +15208,10 @@
       <c r="C1004" s="10"/>
       <c r="D1004" s="27"/>
     </row>
-    <row r="1005" spans="1:1">
+    <row r="1005" spans="1:4">
       <c r="A1005" s="10"/>
     </row>
-    <row r="1006" spans="1:3">
+    <row r="1006" spans="1:4">
       <c r="A1006" s="10"/>
       <c r="C1006" s="10"/>
     </row>
@@ -14614,35 +15231,35 @@
       <c r="C1009" s="10"/>
       <c r="D1009" s="11"/>
     </row>
-    <row r="1010" spans="1:3">
+    <row r="1010" spans="1:4">
       <c r="A1010" s="10"/>
       <c r="B1010" s="10"/>
       <c r="C1010" s="10"/>
     </row>
-    <row r="1011" spans="1:3">
+    <row r="1011" spans="1:4">
       <c r="A1011" s="10"/>
       <c r="B1011" s="10"/>
       <c r="C1011" s="10"/>
     </row>
-    <row r="1012" spans="1:3">
+    <row r="1012" spans="1:4">
       <c r="A1012" s="10"/>
       <c r="B1012" s="10"/>
       <c r="C1012" s="10"/>
     </row>
-    <row r="1013" spans="1:3">
+    <row r="1013" spans="1:4">
       <c r="A1013" s="10"/>
       <c r="C1013" s="10"/>
     </row>
-    <row r="1014" spans="1:3">
+    <row r="1014" spans="1:4">
       <c r="A1014" s="10"/>
       <c r="B1014" s="10"/>
       <c r="C1014" s="10"/>
     </row>
-    <row r="1015" spans="1:3">
+    <row r="1015" spans="1:4">
       <c r="A1015" s="10"/>
       <c r="C1015" s="10"/>
     </row>
-    <row r="1016" spans="1:3">
+    <row r="1016" spans="1:4">
       <c r="A1016" s="10"/>
       <c r="C1016" s="10"/>
     </row>
@@ -14651,11 +15268,11 @@
       <c r="C1017" s="10"/>
       <c r="D1017" s="11"/>
     </row>
-    <row r="1018" spans="1:3">
+    <row r="1018" spans="1:4">
       <c r="A1018" s="10"/>
       <c r="C1018" s="10"/>
     </row>
-    <row r="1019" spans="1:3">
+    <row r="1019" spans="1:4">
       <c r="A1019" s="10"/>
       <c r="C1019" s="10"/>
     </row>
@@ -14665,25 +15282,25 @@
       <c r="C1020" s="10"/>
       <c r="D1020" s="11"/>
     </row>
-    <row r="1022" spans="1:3">
+    <row r="1022" spans="1:4">
       <c r="A1022" s="10"/>
       <c r="C1022" s="10"/>
     </row>
-    <row r="1023" spans="1:3">
+    <row r="1023" spans="1:4">
       <c r="A1023" s="10"/>
       <c r="C1023" s="10"/>
     </row>
-    <row r="1024" spans="1:3">
+    <row r="1024" spans="1:4">
       <c r="A1024" s="10"/>
       <c r="B1024" s="10"/>
       <c r="C1024" s="10"/>
     </row>
-    <row r="1025" spans="1:3">
+    <row r="1025" spans="1:4">
       <c r="A1025" s="10"/>
       <c r="B1025" s="10"/>
       <c r="C1025" s="10"/>
     </row>
-    <row r="1026" spans="1:3">
+    <row r="1026" spans="1:4">
       <c r="A1026" s="10"/>
       <c r="B1026" s="10"/>
       <c r="C1026" s="10"/>
@@ -14693,15 +15310,15 @@
       <c r="C1027" s="10"/>
       <c r="D1027" s="11"/>
     </row>
-    <row r="1028" spans="1:3">
+    <row r="1028" spans="1:4">
       <c r="A1028" s="10"/>
       <c r="C1028" s="10"/>
     </row>
-    <row r="1029" spans="1:3">
+    <row r="1029" spans="1:4">
       <c r="A1029" s="10"/>
       <c r="C1029" s="10"/>
     </row>
-    <row r="1030" spans="1:3">
+    <row r="1030" spans="1:4">
       <c r="A1030" s="10"/>
       <c r="C1030" s="10"/>
     </row>
@@ -14710,27 +15327,27 @@
       <c r="C1031" s="10"/>
       <c r="D1031" s="11"/>
     </row>
-    <row r="1032" spans="1:3">
+    <row r="1032" spans="1:4">
       <c r="A1032" s="10"/>
       <c r="C1032" s="10"/>
     </row>
-    <row r="1033" spans="1:3">
+    <row r="1033" spans="1:4">
       <c r="A1033" s="10"/>
       <c r="C1033" s="10"/>
     </row>
-    <row r="1034" spans="1:3">
+    <row r="1034" spans="1:4">
       <c r="A1034" s="10"/>
       <c r="C1034" s="10"/>
     </row>
-    <row r="1035" spans="1:3">
+    <row r="1035" spans="1:4">
       <c r="A1035" s="10"/>
       <c r="C1035" s="10"/>
     </row>
-    <row r="1036" spans="1:3">
+    <row r="1036" spans="1:4">
       <c r="A1036" s="10"/>
       <c r="C1036" s="10"/>
     </row>
-    <row r="1037" spans="1:3">
+    <row r="1037" spans="1:4">
       <c r="A1037" s="10"/>
       <c r="B1037" s="10"/>
       <c r="C1037" s="10"/>
@@ -14740,33 +15357,33 @@
       <c r="C1038" s="10"/>
       <c r="D1038" s="11"/>
     </row>
-    <row r="1039" spans="2:3">
+    <row r="1039" spans="1:4">
       <c r="B1039" s="10"/>
       <c r="C1039" s="10"/>
     </row>
-    <row r="1040" spans="1:3">
+    <row r="1040" spans="1:4">
       <c r="A1040" s="10"/>
       <c r="B1040" s="10"/>
       <c r="C1040" s="10"/>
     </row>
-    <row r="1041" spans="1:3">
+    <row r="1041" spans="1:4">
       <c r="A1041" s="10"/>
       <c r="C1041" s="10"/>
     </row>
-    <row r="1042" spans="1:3">
+    <row r="1042" spans="1:4">
       <c r="A1042" s="10"/>
       <c r="C1042" s="10"/>
     </row>
-    <row r="1043" spans="1:3">
+    <row r="1043" spans="1:4">
       <c r="A1043" s="10"/>
       <c r="B1043" s="10"/>
       <c r="C1043" s="10"/>
     </row>
-    <row r="1044" spans="1:3">
+    <row r="1044" spans="1:4">
       <c r="A1044" s="10"/>
       <c r="C1044" s="10"/>
     </row>
-    <row r="1045" spans="1:3">
+    <row r="1045" spans="1:4">
       <c r="A1045" s="10"/>
       <c r="C1045" s="10"/>
     </row>
@@ -14776,21 +15393,21 @@
       <c r="C1046" s="10"/>
       <c r="D1046" s="11"/>
     </row>
-    <row r="1047" spans="1:3">
+    <row r="1047" spans="1:4">
       <c r="A1047" s="10"/>
       <c r="B1047" s="10"/>
       <c r="C1047" s="10"/>
     </row>
-    <row r="1048" spans="1:3">
+    <row r="1048" spans="1:4">
       <c r="A1048" s="10"/>
       <c r="B1048" s="10"/>
       <c r="C1048" s="10"/>
     </row>
-    <row r="1049" spans="1:3">
+    <row r="1049" spans="1:4">
       <c r="A1049" s="10"/>
       <c r="C1049" s="10"/>
     </row>
-    <row r="1050" spans="1:3">
+    <row r="1050" spans="1:4">
       <c r="A1050" s="37"/>
       <c r="B1050" s="38"/>
       <c r="C1050" s="10"/>
@@ -14801,24 +15418,24 @@
       <c r="C1051" s="10"/>
       <c r="D1051" s="11"/>
     </row>
-    <row r="1052" spans="1:3">
+    <row r="1052" spans="1:4">
       <c r="A1052" s="10"/>
       <c r="C1052" s="10"/>
     </row>
-    <row r="1053" spans="1:3">
+    <row r="1053" spans="1:4">
       <c r="A1053" s="10"/>
       <c r="C1053" s="10"/>
     </row>
-    <row r="1054" spans="1:3">
+    <row r="1054" spans="1:4">
       <c r="A1054" s="10"/>
       <c r="C1054" s="10"/>
     </row>
-    <row r="1055" spans="1:3">
+    <row r="1055" spans="1:4">
       <c r="A1055" s="10"/>
       <c r="B1055" s="10"/>
       <c r="C1055" s="10"/>
     </row>
-    <row r="1056" spans="1:3">
+    <row r="1056" spans="1:4">
       <c r="A1056" s="10"/>
       <c r="C1056" s="10"/>
     </row>
@@ -14828,11 +15445,11 @@
       <c r="C1057" s="10"/>
       <c r="D1057" s="11"/>
     </row>
-    <row r="1058" spans="1:3">
+    <row r="1058" spans="1:4">
       <c r="A1058" s="10"/>
       <c r="C1058" s="10"/>
     </row>
-    <row r="1059" spans="1:3">
+    <row r="1059" spans="1:4">
       <c r="A1059" s="10"/>
       <c r="B1059" s="10"/>
       <c r="C1059" s="10"/>
@@ -14861,31 +15478,31 @@
       <c r="C1063" s="10"/>
       <c r="D1063" s="11"/>
     </row>
-    <row r="1064" spans="2:3">
+    <row r="1064" spans="1:4">
       <c r="B1064" s="10"/>
       <c r="C1064" s="10"/>
     </row>
-    <row r="1065" spans="1:3">
+    <row r="1065" spans="1:4">
       <c r="A1065" s="10"/>
       <c r="B1065" s="10"/>
       <c r="C1065" s="10"/>
     </row>
-    <row r="1066" spans="1:3">
+    <row r="1066" spans="1:4">
       <c r="A1066" s="10"/>
       <c r="B1066" s="10"/>
       <c r="C1066" s="10"/>
     </row>
-    <row r="1067" spans="1:3">
+    <row r="1067" spans="1:4">
       <c r="A1067" s="10"/>
       <c r="B1067" s="10"/>
       <c r="C1067" s="10"/>
     </row>
-    <row r="1068" spans="1:3">
+    <row r="1068" spans="1:4">
       <c r="A1068" s="10"/>
       <c r="B1068" s="10"/>
       <c r="C1068" s="10"/>
     </row>
-    <row r="1069" spans="1:3">
+    <row r="1069" spans="1:4">
       <c r="A1069" s="10"/>
       <c r="B1069" s="10"/>
       <c r="C1069" s="10"/>
@@ -14902,7 +15519,7 @@
       <c r="C1071" s="10"/>
       <c r="D1071" s="11"/>
     </row>
-    <row r="1072" spans="1:3">
+    <row r="1072" spans="1:4">
       <c r="A1072" s="10"/>
       <c r="B1072" s="10"/>
       <c r="C1072" s="10"/>
@@ -14925,7 +15542,7 @@
       <c r="C1075" s="10"/>
       <c r="D1075" s="11"/>
     </row>
-    <row r="1076" spans="1:3">
+    <row r="1076" spans="1:4">
       <c r="A1076" s="10"/>
       <c r="B1076" s="10"/>
       <c r="C1076" s="10"/>
@@ -14935,30 +15552,30 @@
       <c r="C1077" s="10"/>
       <c r="D1077" s="11"/>
     </row>
-    <row r="1078" spans="1:3">
+    <row r="1078" spans="1:4">
       <c r="A1078" s="10"/>
       <c r="B1078" s="10"/>
       <c r="C1078" s="10"/>
     </row>
-    <row r="1080" spans="1:3">
+    <row r="1080" spans="1:4">
       <c r="A1080" s="10"/>
       <c r="B1080" s="10"/>
       <c r="C1080" s="10"/>
     </row>
-    <row r="1081" spans="1:3">
+    <row r="1081" spans="1:4">
       <c r="A1081" s="10"/>
       <c r="B1081" s="10"/>
       <c r="C1081" s="10"/>
     </row>
-    <row r="1082" spans="1:3">
+    <row r="1082" spans="1:4">
       <c r="A1082" s="10"/>
       <c r="B1082" s="10"/>
       <c r="C1082" s="10"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E680" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:E680">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E728" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:E728">
       <sortCondition ref="B1"/>
     </sortState>
     <extLst/>

--- a/scripts/music.xlsx
+++ b/scripts/music.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14865" windowHeight="14055"/>
+    <workbookView windowWidth="14865" windowHeight="14505"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2493" uniqueCount="1172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2445" uniqueCount="1171">
   <si>
     <t>歌名</t>
   </si>
@@ -3454,9 +3454,6 @@
   </si>
   <si>
     <t>表面的和平</t>
-  </si>
-  <si>
-    <t>new</t>
   </si>
   <si>
     <t>人间惊鸿客</t>
@@ -13095,7 +13092,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="673" spans="1:4">
+    <row r="673" spans="1:3">
       <c r="A673" t="s">
         <v>1099</v>
       </c>
@@ -13106,7 +13103,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="674" spans="1:4">
+    <row r="674" spans="1:3">
       <c r="A674" t="s">
         <v>1100</v>
       </c>
@@ -13117,7 +13114,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="675" spans="1:4">
+    <row r="675" spans="1:3">
       <c r="A675" t="s">
         <v>1101</v>
       </c>
@@ -13128,7 +13125,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="676" spans="1:4">
+    <row r="676" spans="1:3">
       <c r="A676" t="s">
         <v>1103</v>
       </c>
@@ -13139,7 +13136,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="677" spans="1:4">
+    <row r="677" spans="1:3">
       <c r="A677" t="s">
         <v>1105</v>
       </c>
@@ -13150,7 +13147,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="678" spans="1:4">
+    <row r="678" spans="1:3">
       <c r="A678" t="s">
         <v>1107</v>
       </c>
@@ -13161,7 +13158,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="679" spans="1:4">
+    <row r="679" spans="1:3">
       <c r="A679" t="s">
         <v>1109</v>
       </c>
@@ -13172,7 +13169,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="680" spans="1:4">
+    <row r="680" spans="1:3">
       <c r="A680" t="s">
         <v>1110</v>
       </c>
@@ -13183,7 +13180,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="681" spans="1:4">
+    <row r="681" spans="1:3">
       <c r="A681" s="10" t="s">
         <v>1112</v>
       </c>
@@ -13193,27 +13190,21 @@
       <c r="C681" t="s">
         <v>258</v>
       </c>
-      <c r="D681" s="2" t="s">
+    </row>
+    <row r="682" spans="1:3">
+      <c r="A682" s="10" t="s">
         <v>1113</v>
       </c>
-    </row>
-    <row r="682" spans="1:4">
-      <c r="A682" s="10" t="s">
+      <c r="B682" s="10" t="s">
         <v>1114</v>
       </c>
-      <c r="B682" s="10" t="s">
+      <c r="C682" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="683" spans="1:3">
+      <c r="A683" s="10" t="s">
         <v>1115</v>
-      </c>
-      <c r="C682" t="s">
-        <v>258</v>
-      </c>
-      <c r="D682" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="683" spans="1:4">
-      <c r="A683" s="10" t="s">
-        <v>1116</v>
       </c>
       <c r="B683" t="s">
         <v>263</v>
@@ -13221,13 +13212,10 @@
       <c r="C683" t="s">
         <v>258</v>
       </c>
-      <c r="D683" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="684" spans="1:4">
+    </row>
+    <row r="684" spans="1:3">
       <c r="A684" s="10" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="B684" s="10" t="s">
         <v>324</v>
@@ -13235,13 +13223,10 @@
       <c r="C684" t="s">
         <v>258</v>
       </c>
-      <c r="D684" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="685" spans="1:4">
+    </row>
+    <row r="685" spans="1:3">
       <c r="A685" s="10" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="B685" s="10" t="s">
         <v>1023</v>
@@ -13249,13 +13234,10 @@
       <c r="C685" t="s">
         <v>258</v>
       </c>
-      <c r="D685" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="686" spans="1:4">
+    </row>
+    <row r="686" spans="1:3">
       <c r="A686" s="10" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B686" t="s">
         <v>263</v>
@@ -13263,13 +13245,10 @@
       <c r="C686" t="s">
         <v>258</v>
       </c>
-      <c r="D686" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="687" spans="1:4">
+    </row>
+    <row r="687" spans="1:3">
       <c r="A687" s="10" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="B687" t="s">
         <v>324</v>
@@ -13277,13 +13256,10 @@
       <c r="C687" t="s">
         <v>258</v>
       </c>
-      <c r="D687" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="688" spans="1:4">
+    </row>
+    <row r="688" spans="1:3">
       <c r="A688" s="10" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="B688" t="s">
         <v>263</v>
@@ -13291,13 +13267,10 @@
       <c r="C688" t="s">
         <v>258</v>
       </c>
-      <c r="D688" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="689" spans="1:4">
+    </row>
+    <row r="689" spans="1:3">
       <c r="A689" s="10" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="B689" t="s">
         <v>263</v>
@@ -13305,13 +13278,10 @@
       <c r="C689" t="s">
         <v>258</v>
       </c>
-      <c r="D689" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="690" spans="1:4">
+    </row>
+    <row r="690" spans="1:3">
       <c r="A690" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B690" t="s">
         <v>1066</v>
@@ -13319,13 +13289,10 @@
       <c r="C690" t="s">
         <v>258</v>
       </c>
-      <c r="D690" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="691" spans="1:4">
+    </row>
+    <row r="691" spans="1:3">
       <c r="A691" s="10" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B691" s="10" t="s">
         <v>324</v>
@@ -13333,27 +13300,21 @@
       <c r="C691" t="s">
         <v>258</v>
       </c>
-      <c r="D691" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="692" spans="1:4">
+    </row>
+    <row r="692" spans="1:3">
       <c r="A692" s="10" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B692" s="10" t="s">
         <v>1125</v>
       </c>
-      <c r="B692" s="10" t="s">
+      <c r="C692" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="693" spans="1:3">
+      <c r="A693" s="10" t="s">
         <v>1126</v>
-      </c>
-      <c r="C692" t="s">
-        <v>258</v>
-      </c>
-      <c r="D692" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="693" spans="1:4">
-      <c r="A693" s="10" t="s">
-        <v>1127</v>
       </c>
       <c r="B693" s="10" t="s">
         <v>865</v>
@@ -13361,13 +13322,10 @@
       <c r="C693" t="s">
         <v>258</v>
       </c>
-      <c r="D693" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="694" spans="1:4">
+    </row>
+    <row r="694" spans="1:3">
       <c r="A694" s="10" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B694" s="10" t="s">
         <v>324</v>
@@ -13375,13 +13333,10 @@
       <c r="C694" t="s">
         <v>258</v>
       </c>
-      <c r="D694" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="695" spans="1:4">
+    </row>
+    <row r="695" spans="1:3">
       <c r="A695" s="10" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B695" s="10" t="s">
         <v>324</v>
@@ -13389,13 +13344,10 @@
       <c r="C695" t="s">
         <v>258</v>
       </c>
-      <c r="D695" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="696" spans="1:4">
+    </row>
+    <row r="696" spans="1:3">
       <c r="A696" s="10" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B696" t="s">
         <v>1023</v>
@@ -13403,13 +13355,10 @@
       <c r="C696" t="s">
         <v>258</v>
       </c>
-      <c r="D696" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="697" spans="1:4">
+    </row>
+    <row r="697" spans="1:3">
       <c r="A697" s="10" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B697" s="10" t="s">
         <v>324</v>
@@ -13417,13 +13366,10 @@
       <c r="C697" t="s">
         <v>258</v>
       </c>
-      <c r="D697" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="698" spans="1:4">
+    </row>
+    <row r="698" spans="1:3">
       <c r="A698" s="10" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B698" s="10" t="s">
         <v>324</v>
@@ -13431,13 +13377,10 @@
       <c r="C698" t="s">
         <v>258</v>
       </c>
-      <c r="D698" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="699" spans="1:4">
+    </row>
+    <row r="699" spans="1:3">
       <c r="A699" s="10" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B699" s="10" t="s">
         <v>324</v>
@@ -13445,13 +13388,10 @@
       <c r="C699" t="s">
         <v>258</v>
       </c>
-      <c r="D699" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="700" spans="1:4">
+    </row>
+    <row r="700" spans="1:3">
       <c r="A700" s="10" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B700" s="10" t="s">
         <v>324</v>
@@ -13459,13 +13399,10 @@
       <c r="C700" t="s">
         <v>258</v>
       </c>
-      <c r="D700" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="701" spans="1:4">
+    </row>
+    <row r="701" spans="1:3">
       <c r="A701" s="10" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B701" s="10" t="s">
         <v>324</v>
@@ -13473,27 +13410,21 @@
       <c r="C701" t="s">
         <v>258</v>
       </c>
-      <c r="D701" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="702" spans="1:4">
+    </row>
+    <row r="702" spans="1:3">
       <c r="A702" s="10" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B702" s="10" t="s">
         <v>1136</v>
       </c>
-      <c r="B702" s="10" t="s">
+      <c r="C702" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="703" spans="1:3">
+      <c r="A703" s="10" t="s">
         <v>1137</v>
-      </c>
-      <c r="C702" t="s">
-        <v>258</v>
-      </c>
-      <c r="D702" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="703" spans="1:4">
-      <c r="A703" s="10" t="s">
-        <v>1138</v>
       </c>
       <c r="B703" t="s">
         <v>324</v>
@@ -13501,13 +13432,10 @@
       <c r="C703" t="s">
         <v>258</v>
       </c>
-      <c r="D703" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="704" spans="1:4">
+    </row>
+    <row r="704" spans="1:3">
       <c r="A704" s="10" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="B704" t="s">
         <v>324</v>
@@ -13515,13 +13443,10 @@
       <c r="C704" t="s">
         <v>258</v>
       </c>
-      <c r="D704" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="705" spans="1:4">
+    </row>
+    <row r="705" spans="1:3">
       <c r="A705" s="10" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="B705" t="s">
         <v>324</v>
@@ -13529,13 +13454,10 @@
       <c r="C705" t="s">
         <v>258</v>
       </c>
-      <c r="D705" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="706" spans="1:4">
+    </row>
+    <row r="706" spans="1:3">
       <c r="A706" s="10" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="B706" t="s">
         <v>324</v>
@@ -13543,13 +13465,10 @@
       <c r="C706" t="s">
         <v>258</v>
       </c>
-      <c r="D706" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="707" spans="1:4">
+    </row>
+    <row r="707" spans="1:3">
       <c r="A707" s="10" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="B707" t="s">
         <v>324</v>
@@ -13557,13 +13476,10 @@
       <c r="C707" t="s">
         <v>258</v>
       </c>
-      <c r="D707" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="708" spans="1:4">
+    </row>
+    <row r="708" spans="1:3">
       <c r="A708" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="B708" t="s">
         <v>324</v>
@@ -13571,13 +13487,10 @@
       <c r="C708" t="s">
         <v>258</v>
       </c>
-      <c r="D708" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="709" spans="1:4">
+    </row>
+    <row r="709" spans="1:3">
       <c r="A709" s="10" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B709" s="10" t="s">
         <v>731</v>
@@ -13585,13 +13498,10 @@
       <c r="C709" t="s">
         <v>258</v>
       </c>
-      <c r="D709" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="710" spans="1:4">
+    </row>
+    <row r="710" spans="1:3">
       <c r="A710" s="10" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="B710" t="s">
         <v>324</v>
@@ -13599,41 +13509,32 @@
       <c r="C710" t="s">
         <v>258</v>
       </c>
-      <c r="D710" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="711" spans="1:4">
+    </row>
+    <row r="711" spans="1:3">
       <c r="A711" s="10" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B711" t="s">
         <v>1146</v>
       </c>
-      <c r="B711" t="s">
+      <c r="C711" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="712" spans="1:3">
+      <c r="A712" s="10" t="s">
         <v>1147</v>
       </c>
-      <c r="C711" t="s">
-        <v>258</v>
-      </c>
-      <c r="D711" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="712" spans="1:4">
-      <c r="A712" s="10" t="s">
+      <c r="B712" t="s">
         <v>1148</v>
       </c>
-      <c r="B712" t="s">
+      <c r="C712" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="713" spans="1:3">
+      <c r="A713" s="10" t="s">
         <v>1149</v>
-      </c>
-      <c r="C712" t="s">
-        <v>258</v>
-      </c>
-      <c r="D712" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="713" spans="1:4">
-      <c r="A713" s="10" t="s">
-        <v>1150</v>
       </c>
       <c r="B713" t="s">
         <v>464</v>
@@ -13641,27 +13542,21 @@
       <c r="C713" t="s">
         <v>258</v>
       </c>
-      <c r="D713" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="714" spans="1:4">
+    </row>
+    <row r="714" spans="1:3">
       <c r="A714" s="10" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B714" t="s">
         <v>1151</v>
       </c>
-      <c r="B714" t="s">
+      <c r="C714" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="715" spans="1:3">
+      <c r="A715" s="10" t="s">
         <v>1152</v>
-      </c>
-      <c r="C714" t="s">
-        <v>258</v>
-      </c>
-      <c r="D714" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="715" spans="1:4">
-      <c r="A715" s="10" t="s">
-        <v>1153</v>
       </c>
       <c r="B715" t="s">
         <v>985</v>
@@ -13669,41 +13564,32 @@
       <c r="C715" t="s">
         <v>258</v>
       </c>
-      <c r="D715" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="716" spans="1:4">
+    </row>
+    <row r="716" spans="1:3">
       <c r="A716" s="10" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B716" s="10" t="s">
         <v>1154</v>
       </c>
-      <c r="B716" s="10" t="s">
+      <c r="C716" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="717" spans="1:3">
+      <c r="A717" s="10" t="s">
         <v>1155</v>
       </c>
-      <c r="C716" t="s">
-        <v>258</v>
-      </c>
-      <c r="D716" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="717" spans="1:4">
-      <c r="A717" s="10" t="s">
+      <c r="B717" s="10" t="s">
         <v>1156</v>
       </c>
-      <c r="B717" s="10" t="s">
+      <c r="C717" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="718" spans="1:3">
+      <c r="A718" s="10" t="s">
         <v>1157</v>
-      </c>
-      <c r="C717" t="s">
-        <v>258</v>
-      </c>
-      <c r="D717" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="718" spans="1:4">
-      <c r="A718" s="10" t="s">
-        <v>1158</v>
       </c>
       <c r="B718" t="s">
         <v>324</v>
@@ -13711,13 +13597,10 @@
       <c r="C718" t="s">
         <v>258</v>
       </c>
-      <c r="D718" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="719" spans="1:4">
+    </row>
+    <row r="719" spans="1:3">
       <c r="A719" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B719" s="20" t="s">
         <v>856</v>
@@ -13725,13 +13608,10 @@
       <c r="C719" t="s">
         <v>258</v>
       </c>
-      <c r="D719" s="2" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="720" spans="1:4">
+    </row>
+    <row r="720" spans="1:3">
       <c r="A720" s="10" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B720" s="10" t="s">
         <v>464</v>
@@ -13739,27 +13619,21 @@
       <c r="C720" t="s">
         <v>258</v>
       </c>
-      <c r="D720" s="2" t="s">
-        <v>1113</v>
-      </c>
     </row>
     <row r="721" spans="1:4">
       <c r="A721" s="10" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B721" t="s">
         <v>1161</v>
       </c>
-      <c r="B721" t="s">
-        <v>1162</v>
-      </c>
       <c r="C721" t="s">
         <v>258</v>
-      </c>
-      <c r="D721" s="2" t="s">
-        <v>1113</v>
       </c>
     </row>
     <row r="722" spans="1:4">
       <c r="A722" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B722" t="s">
         <v>324</v>
@@ -13767,27 +13641,21 @@
       <c r="C722" t="s">
         <v>258</v>
       </c>
-      <c r="D722" s="2" t="s">
-        <v>1113</v>
-      </c>
     </row>
     <row r="723" spans="1:4">
       <c r="A723" s="10" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B723" s="10" t="s">
         <v>1164</v>
       </c>
-      <c r="B723" s="10" t="s">
-        <v>1165</v>
-      </c>
       <c r="C723" t="s">
         <v>258</v>
-      </c>
-      <c r="D723" s="2" t="s">
-        <v>1113</v>
       </c>
     </row>
     <row r="724" spans="1:4">
       <c r="A724" s="10" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B724" t="s">
         <v>1023</v>
@@ -13795,27 +13663,21 @@
       <c r="C724" t="s">
         <v>258</v>
       </c>
-      <c r="D724" s="2" t="s">
-        <v>1113</v>
-      </c>
     </row>
     <row r="725" spans="1:4">
       <c r="A725" s="10" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B725" t="s">
         <v>1167</v>
       </c>
-      <c r="B725" t="s">
-        <v>1168</v>
-      </c>
       <c r="C725" t="s">
         <v>258</v>
-      </c>
-      <c r="D725" s="2" t="s">
-        <v>1113</v>
       </c>
     </row>
     <row r="726" spans="1:4">
       <c r="A726" s="10" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B726" t="s">
         <v>263</v>
@@ -13823,13 +13685,10 @@
       <c r="C726" t="s">
         <v>258</v>
       </c>
-      <c r="D726" s="2" t="s">
-        <v>1113</v>
-      </c>
     </row>
     <row r="727" spans="1:4">
       <c r="A727" s="10" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="B727" t="s">
         <v>263</v>
@@ -13837,22 +13696,16 @@
       <c r="C727" t="s">
         <v>258</v>
       </c>
-      <c r="D727" s="2" t="s">
-        <v>1113</v>
-      </c>
     </row>
     <row r="728" spans="1:4">
       <c r="A728" s="10" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B728" s="21" t="s">
         <v>285</v>
       </c>
       <c r="C728" t="s">
         <v>258</v>
-      </c>
-      <c r="D728" s="2" t="s">
-        <v>1113</v>
       </c>
     </row>
     <row r="729" spans="1:4">
